--- a/btc.xlsx
+++ b/btc.xlsx
@@ -1127,10 +1127,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH738"/>
+  <dimension ref="A1:AH766"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="29.3636363636364" customWidth="1"/>
+    <col min="1" max="1" width="27.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
@@ -75870,7 +75870,7 @@
         <v>0.533868745689323</v>
       </c>
       <c r="V719">
-        <v>0.533706530638577</v>
+        <v>0.533706530638578</v>
       </c>
       <c r="W719">
         <v>0.232245506868338</v>
@@ -75974,7 +75974,7 @@
         <v>0.475243162849044</v>
       </c>
       <c r="V720">
-        <v>0.475243180626404</v>
+        <v>0.475243180626403</v>
       </c>
       <c r="W720">
         <v>0.552978456960323</v>
@@ -76078,7 +76078,7 @@
         <v>0.453387381597077</v>
       </c>
       <c r="V721">
-        <v>0.453449693488718</v>
+        <v>0.453449693488716</v>
       </c>
       <c r="W721">
         <v>0.449834500770513</v>
@@ -76182,7 +76182,7 @@
         <v>0.49917776872642</v>
       </c>
       <c r="V722">
-        <v>0.499299033553064</v>
+        <v>0.499299033553063</v>
       </c>
       <c r="W722">
         <v>0.16582127376985</v>
@@ -76390,7 +76390,7 @@
         <v>0.514965711845142</v>
       </c>
       <c r="V724">
-        <v>0.515404174700136</v>
+        <v>0.515404174700138</v>
       </c>
       <c r="W724">
         <v>0.863303829724577</v>
@@ -76494,7 +76494,7 @@
         <v>0.433785700142215</v>
       </c>
       <c r="V725">
-        <v>0.433844104173584</v>
+        <v>0.433844104173583</v>
       </c>
       <c r="W725">
         <v>1.22159325469879</v>
@@ -76598,7 +76598,7 @@
         <v>0.397558183722288</v>
       </c>
       <c r="V726">
-        <v>0.39850835685052</v>
+        <v>0.398508356850519</v>
       </c>
       <c r="W726">
         <v>0.957452167415522</v>
@@ -76702,7 +76702,7 @@
         <v>0.457178690561151</v>
       </c>
       <c r="V727">
-        <v>0.457452450660725</v>
+        <v>0.457452450660726</v>
       </c>
       <c r="W727">
         <v>0.614631530725738</v>
@@ -76806,7 +76806,7 @@
         <v>0.509607130346639</v>
       </c>
       <c r="V728">
-        <v>0.509814011880484</v>
+        <v>0.509814011880486</v>
       </c>
       <c r="W728">
         <v>0.346407203684088</v>
@@ -77014,7 +77014,7 @@
         <v>0.424346999291529</v>
       </c>
       <c r="V730">
-        <v>0.425120435080488</v>
+        <v>0.425120435080487</v>
       </c>
       <c r="W730">
         <v>0.796906416586549</v>
@@ -77159,103 +77159,103 @@
     </row>
     <row r="732" spans="1:34">
       <c r="A732" s="2">
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="B732">
-        <v>67643.39</v>
+        <v>67975.93</v>
       </c>
       <c r="C732">
-        <v>67684.86</v>
+        <v>68245</v>
       </c>
       <c r="D732">
-        <v>63888.79</v>
+        <v>67190</v>
       </c>
       <c r="E732">
-        <v>64656.02</v>
+        <v>67643.4</v>
       </c>
       <c r="F732">
-        <v>33075.90923</v>
+        <v>8175.13484</v>
       </c>
       <c r="G732">
-        <v>8268695</v>
+        <v>2160900</v>
       </c>
       <c r="H732">
-        <v>16388.63858</v>
+        <v>3974.29287</v>
       </c>
       <c r="I732">
-        <v>1069328860.05896</v>
+        <v>269081093.610938</v>
       </c>
       <c r="J732">
-        <v>2158158656.12152</v>
+        <v>553613335.577414</v>
       </c>
       <c r="K732">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L732">
-        <v>0.363201168708008</v>
+        <v>0.4409939803091</v>
       </c>
       <c r="M732">
-        <v>1.62675523545743</v>
+        <v>1.58349121077101</v>
       </c>
       <c r="N732">
-        <v>-0.313215888123346</v>
+        <v>-0.203066645527713</v>
       </c>
       <c r="O732">
-        <v>1.51727242007695</v>
+        <v>1.73348609755212</v>
       </c>
       <c r="P732">
-        <v>0.28243776760112</v>
+        <v>0.291470377157383</v>
       </c>
       <c r="Q732">
-        <v>-1.14509083939175</v>
+        <v>-1.29092903544521</v>
       </c>
       <c r="R732">
-        <v>1.12920029809499</v>
+        <v>0.287235663888698</v>
       </c>
       <c r="S732">
-        <v>0.503906107211419</v>
+        <v>-1.52015840702789</v>
       </c>
       <c r="T732">
-        <v>0.589269544649071</v>
+        <v>-1.26999436395892</v>
       </c>
       <c r="U732">
-        <v>0.495485655920697</v>
+        <v>0.486144014475974</v>
       </c>
       <c r="V732">
-        <v>0.495482043002659</v>
+        <v>0.486045180487368</v>
       </c>
       <c r="W732">
-        <v>-0.210759565000652</v>
+        <v>0.747248137064393</v>
       </c>
       <c r="X732">
-        <v>-0.819133166507176</v>
+        <v>-0.384629011364412</v>
       </c>
       <c r="Y732">
-        <v>-0.901113128555334</v>
+        <v>-0.444223596896747</v>
       </c>
       <c r="Z732">
-        <v>-1.01431017002456</v>
+        <v>-0.627640233008148</v>
       </c>
       <c r="AA732">
-        <v>-0.273736690947443</v>
+        <v>-0.687234435167795</v>
       </c>
       <c r="AB732">
         <v>0.09</v>
       </c>
       <c r="AC732">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AD732">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE732">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF732">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AG732">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH732">
         <v>10</v>
@@ -77263,88 +77263,88 @@
     </row>
     <row r="733" spans="1:34">
       <c r="A733" s="2">
-        <v>46078</v>
+        <v>46076</v>
       </c>
       <c r="B733">
-        <v>64058.15</v>
+        <v>67643.39</v>
       </c>
       <c r="C733">
-        <v>69988.83</v>
+        <v>67684.86</v>
       </c>
       <c r="D733">
-        <v>63913.27</v>
+        <v>63888.79</v>
       </c>
       <c r="E733">
-        <v>67988.04</v>
+        <v>64656.02</v>
       </c>
       <c r="F733">
-        <v>30749.99259</v>
+        <v>33075.90923</v>
       </c>
       <c r="G733">
-        <v>7096715</v>
+        <v>8268695</v>
       </c>
       <c r="H733">
-        <v>16382.91985</v>
+        <v>16388.63858</v>
       </c>
       <c r="I733">
-        <v>1098904977.00827</v>
+        <v>1069328860.05896</v>
       </c>
       <c r="J733">
-        <v>2064089702.84443</v>
+        <v>2158158656.12152</v>
       </c>
       <c r="K733">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L733">
-        <v>0.439083926108241</v>
+        <v>0.321492971535063</v>
       </c>
       <c r="M733">
-        <v>1.32331087061611</v>
+        <v>1.32426858241971</v>
       </c>
       <c r="N733">
-        <v>-0.112281127758788</v>
+        <v>-0.156534928138942</v>
       </c>
       <c r="O733">
-        <v>1.58903636452491</v>
+        <v>1.44836981949415</v>
       </c>
       <c r="P733">
-        <v>0.763099675014892</v>
+        <v>0.725362406459042</v>
       </c>
       <c r="Q733">
-        <v>-1.19443147402183</v>
+        <v>-1.18131635366167</v>
       </c>
       <c r="R733">
-        <v>1.03006437952708</v>
+        <v>1.1366291610018</v>
       </c>
       <c r="S733">
-        <v>0.354313487945936</v>
+        <v>0.513714200251819</v>
       </c>
       <c r="T733">
-        <v>0.188830757922067</v>
+        <v>0.600087275293198</v>
       </c>
       <c r="U733">
-        <v>0.532778009687319</v>
+        <v>0.495485655920697</v>
       </c>
       <c r="V733">
-        <v>0.532392063917531</v>
+        <v>0.495482043002657</v>
       </c>
       <c r="W733">
-        <v>1.08709950319641</v>
+        <v>-0.163216645593054</v>
       </c>
       <c r="X733">
-        <v>-0.191143953267777</v>
+        <v>-0.734982718335913</v>
       </c>
       <c r="Y733">
-        <v>-0.275320257455588</v>
+        <v>-0.839519693490251</v>
       </c>
       <c r="Z733">
-        <v>-0.485395870787872</v>
+        <v>-0.96296394837538</v>
       </c>
       <c r="AA733">
-        <v>-0.123325344213475</v>
+        <v>-0.503921680174711</v>
       </c>
       <c r="AB733">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AC733">
         <v>9</v>
@@ -77367,94 +77367,94 @@
     </row>
     <row r="734" spans="1:34">
       <c r="A734" s="2">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="B734">
-        <v>67485.19</v>
+        <v>64656.01</v>
       </c>
       <c r="C734">
-        <v>68216.8</v>
+        <v>65026.75</v>
       </c>
       <c r="D734">
-        <v>64914.46</v>
+        <v>62510.28</v>
       </c>
       <c r="E734">
-        <v>65872.1</v>
+        <v>64058.15</v>
       </c>
       <c r="F734">
-        <v>21228.58424</v>
+        <v>23102.83622</v>
       </c>
       <c r="G734">
-        <v>3856064</v>
+        <v>7553629</v>
       </c>
       <c r="H734">
-        <v>10107.20917</v>
+        <v>11150.61026</v>
       </c>
       <c r="I734">
-        <v>671986242.524662</v>
+        <v>709235431.917698</v>
       </c>
       <c r="J734">
-        <v>1412033823.56197</v>
+        <v>1469512159.71993</v>
       </c>
       <c r="K734">
         <v>11</v>
       </c>
       <c r="L734">
-        <v>0.399149011419644</v>
+        <v>0.313495011788756</v>
       </c>
       <c r="M734">
-        <v>1.13416296029811</v>
+        <v>1.18624308977613</v>
       </c>
       <c r="N734">
-        <v>0.00722868950277784</v>
+        <v>-0.105660235907003</v>
       </c>
       <c r="O734">
-        <v>1.44771890667251</v>
+        <v>1.23555609035077</v>
       </c>
       <c r="P734">
-        <v>1.10945479842111</v>
+        <v>0.98606868083531</v>
       </c>
       <c r="Q734">
-        <v>-1.20151585634761</v>
+        <v>-1.08326892765034</v>
       </c>
       <c r="R734">
-        <v>0.697867251553453</v>
+        <v>0.777108997717004</v>
       </c>
       <c r="S734">
-        <v>-0.357641221060333</v>
+        <v>-0.120817895670736</v>
       </c>
       <c r="T734">
-        <v>-0.925393150499576</v>
+        <v>0.324623801605707</v>
       </c>
       <c r="U734">
-        <v>0.476113199812707</v>
+        <v>0.482651140916931</v>
       </c>
       <c r="V734">
-        <v>0.475899536761464</v>
+        <v>0.482633251604307</v>
       </c>
       <c r="W734">
-        <v>0.366780639268095</v>
+        <v>-0.190390504620149</v>
       </c>
       <c r="X734">
-        <v>-0.417394814821354</v>
+        <v>-0.713299069637846</v>
       </c>
       <c r="Y734">
-        <v>-0.547277410027617</v>
+        <v>-0.851833598627039</v>
       </c>
       <c r="Z734">
-        <v>-0.716346136465394</v>
+        <v>-0.972123052971169</v>
       </c>
       <c r="AA734">
-        <v>-0.102989694507966</v>
+        <v>-0.564864516416134</v>
       </c>
       <c r="AB734">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="AC734">
         <v>9</v>
       </c>
       <c r="AD734">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE734">
         <v>7</v>
@@ -77471,85 +77471,85 @@
     </row>
     <row r="735" spans="1:34">
       <c r="A735" s="2">
-        <v>46082</v>
+        <v>46078</v>
       </c>
       <c r="B735">
-        <v>66973.26</v>
+        <v>64058.15</v>
       </c>
       <c r="C735">
-        <v>68199.99</v>
+        <v>69988.83</v>
       </c>
       <c r="D735">
-        <v>65056</v>
+        <v>63913.27</v>
       </c>
       <c r="E735">
-        <v>65776.47</v>
+        <v>67988.04</v>
       </c>
       <c r="F735">
-        <v>23201.85859</v>
+        <v>30749.99259</v>
       </c>
       <c r="G735">
-        <v>5312013</v>
+        <v>7096715</v>
       </c>
       <c r="H735">
-        <v>11209.77201</v>
+        <v>16382.91985</v>
       </c>
       <c r="I735">
-        <v>747161922.848462</v>
+        <v>1098904977.00827</v>
       </c>
       <c r="J735">
-        <v>1545783742.9062</v>
+        <v>2064089702.84443</v>
       </c>
       <c r="K735">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L735">
-        <v>0.423181461808542</v>
+        <v>0.477466128547517</v>
       </c>
       <c r="M735">
-        <v>1.03238762354466</v>
+        <v>1.0720179904488</v>
       </c>
       <c r="N735">
-        <v>0.141085088091792</v>
+        <v>0.14889696567492</v>
       </c>
       <c r="O735">
-        <v>1.3359836365234</v>
+        <v>1.37702137735869</v>
       </c>
       <c r="P735">
-        <v>1.15941292978295</v>
+        <v>1.18774162308175</v>
       </c>
       <c r="Q735">
-        <v>-1.15511373493413</v>
+        <v>-1.07689598039047</v>
       </c>
       <c r="R735">
-        <v>0.755471695149935</v>
+        <v>1.01574512058195</v>
       </c>
       <c r="S735">
-        <v>-0.229412883005087</v>
+        <v>0.327304169371144</v>
       </c>
       <c r="T735">
-        <v>-0.459438579787719</v>
+        <v>0.139773523717724</v>
       </c>
       <c r="U735">
-        <v>0.483141122790543</v>
+        <v>0.532778009687319</v>
       </c>
       <c r="V735">
-        <v>0.483354755331904</v>
+        <v>0.532392063917531</v>
       </c>
       <c r="W735">
-        <v>0.352995095251395</v>
+        <v>1.18807425296431</v>
       </c>
       <c r="X735">
-        <v>-0.301057336597737</v>
+        <v>0.108999502552618</v>
       </c>
       <c r="Y735">
-        <v>-0.476688924480302</v>
+        <v>-0.0591681805808034</v>
       </c>
       <c r="Z735">
-        <v>-0.654206969405642</v>
+        <v>-0.301551097770688</v>
       </c>
       <c r="AA735">
-        <v>-0.185719370722099</v>
+        <v>-0.387425986057188</v>
       </c>
       <c r="AB735">
         <v>0.11</v>
@@ -77564,7 +77564,7 @@
         <v>7</v>
       </c>
       <c r="AF735">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG735">
         <v>1</v>
@@ -77575,97 +77575,97 @@
     </row>
     <row r="736" spans="1:34">
       <c r="A736" s="2">
-        <v>46083</v>
+        <v>46079</v>
       </c>
       <c r="B736">
-        <v>65776.48</v>
+        <v>67988.04</v>
       </c>
       <c r="C736">
-        <v>70096</v>
+        <v>68860</v>
       </c>
       <c r="D736">
-        <v>65259.21</v>
+        <v>66500</v>
       </c>
       <c r="E736">
-        <v>68830.06</v>
+        <v>67485.18</v>
       </c>
       <c r="F736">
-        <v>32010.38431</v>
+        <v>20737.77792</v>
       </c>
       <c r="G736">
-        <v>8397526</v>
+        <v>5426137</v>
       </c>
       <c r="H736">
-        <v>15335.91369</v>
+        <v>10172.50047</v>
       </c>
       <c r="I736">
-        <v>1037871544.54815</v>
+        <v>689304052.453067</v>
       </c>
       <c r="J736">
-        <v>2164578841.84592</v>
+        <v>1404774665.56456</v>
       </c>
       <c r="K736">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L736">
-        <v>0.541131634221866</v>
+        <v>0.511389569320065</v>
       </c>
       <c r="M736">
-        <v>0.92771602479471</v>
+        <v>0.971710204051099</v>
       </c>
       <c r="N736">
-        <v>0.443419142665624</v>
+        <v>0.386803812664407</v>
       </c>
       <c r="O736">
-        <v>1.45122683968629</v>
+        <v>1.3934946703241</v>
       </c>
       <c r="P736">
-        <v>1.37780923351373</v>
+        <v>1.31152040533872</v>
       </c>
       <c r="Q736">
-        <v>-1.09343033616525</v>
+        <v>-1.0471121001014</v>
       </c>
       <c r="R736">
-        <v>1.02641644354847</v>
+        <v>0.682784151356496</v>
       </c>
       <c r="S736">
-        <v>0.332679733112782</v>
+        <v>-0.362830224077292</v>
       </c>
       <c r="T736">
-        <v>0.55275414152664</v>
+        <v>-0.425943639485784</v>
       </c>
       <c r="U736">
-        <v>0.479091832871531</v>
+        <v>0.490529916427999</v>
       </c>
       <c r="V736">
-        <v>0.47947966804622</v>
+        <v>0.490686563012613</v>
       </c>
       <c r="W736">
-        <v>1.35866504820367</v>
+        <v>0.948982045959133</v>
       </c>
       <c r="X736">
-        <v>0.438493716028249</v>
+        <v>0.178620830479431</v>
       </c>
       <c r="Y736">
-        <v>0.217991214483627</v>
+        <v>-0.046870987161557</v>
       </c>
       <c r="Z736">
-        <v>-0.0738103564956194</v>
+        <v>-0.297244091669791</v>
       </c>
       <c r="AA736">
-        <v>-0.215807645093133</v>
+        <v>-0.521308430654726</v>
       </c>
       <c r="AB736">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="AC736">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AD736">
         <v>3</v>
       </c>
       <c r="AE736">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF736">
         <v>0</v>
@@ -77679,91 +77679,91 @@
     </row>
     <row r="737" spans="1:34">
       <c r="A737" s="2">
-        <v>46108</v>
+        <v>46080</v>
       </c>
       <c r="B737">
-        <v>68820.31</v>
+        <v>67485.19</v>
       </c>
       <c r="C737">
-        <v>69179.05</v>
+        <v>68216.8</v>
       </c>
       <c r="D737">
-        <v>65548.25</v>
+        <v>64914.46</v>
       </c>
       <c r="E737">
-        <v>66407.28</v>
+        <v>65872.1</v>
       </c>
       <c r="F737">
-        <v>28603.69557</v>
+        <v>21228.58424</v>
       </c>
       <c r="G737">
-        <v>4159306</v>
+        <v>3856064</v>
       </c>
       <c r="H737">
-        <v>14568.62853</v>
+        <v>10107.20917</v>
       </c>
       <c r="I737">
-        <v>976680026.265681</v>
+        <v>671986242.524662</v>
       </c>
       <c r="J737">
-        <v>1917318222.70991</v>
+        <v>1412033823.56197</v>
       </c>
       <c r="K737">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L737">
-        <v>0.502955719122897</v>
+        <v>0.48917526135817</v>
       </c>
       <c r="M737">
-        <v>0.985128956285769</v>
+        <v>1.04551323869686</v>
       </c>
       <c r="N737">
-        <v>0.634453456850784</v>
+        <v>0.563730307584649</v>
       </c>
       <c r="O737">
-        <v>1.32351989813258</v>
+        <v>1.26941253020361</v>
       </c>
       <c r="P737">
-        <v>1.34481121040245</v>
+        <v>1.27097921868851</v>
       </c>
       <c r="Q737">
-        <v>-1.06521764627302</v>
+        <v>-1.00813300026643</v>
       </c>
       <c r="R737">
-        <v>0.902253918744731</v>
+        <v>0.692782760815087</v>
       </c>
       <c r="S737">
-        <v>0.0767587414932539</v>
+        <v>-0.357893355505746</v>
       </c>
       <c r="T737">
-        <v>-0.903030724482768</v>
+        <v>-0.953036740670965</v>
       </c>
       <c r="U737">
-        <v>0.509326792908529</v>
+        <v>0.476113199812707</v>
       </c>
       <c r="V737">
-        <v>0.509399021350381</v>
+        <v>0.475899536761465</v>
       </c>
       <c r="W737">
-        <v>0.553083642327539</v>
+        <v>0.471896628251117</v>
       </c>
       <c r="X737">
-        <v>0.129436661072653</v>
+        <v>0.0263694427928636</v>
       </c>
       <c r="Y737">
-        <v>-0.166616637860102</v>
+        <v>-0.272818582924924</v>
       </c>
       <c r="Z737">
-        <v>-0.411202289410712</v>
+        <v>-0.499833337783221</v>
       </c>
       <c r="AA737">
-        <v>-0.157172345304847</v>
+        <v>-0.492404484562408</v>
       </c>
       <c r="AB737">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AC737">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AD737">
         <v>3</v>
@@ -77772,7 +77772,7 @@
         <v>7</v>
       </c>
       <c r="AF737">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG737">
         <v>1</v>
@@ -77783,106 +77783,3018 @@
     </row>
     <row r="738" spans="1:34">
       <c r="A738" s="2">
-        <v>46109</v>
+        <v>46081</v>
       </c>
       <c r="B738">
-        <v>66407.28</v>
+        <v>65872.09</v>
       </c>
       <c r="C738">
-        <v>67288.94</v>
+        <v>67760</v>
       </c>
       <c r="D738">
-        <v>65932.09</v>
+        <v>63030</v>
       </c>
       <c r="E738">
-        <v>66377.03</v>
+        <v>66973.26</v>
       </c>
       <c r="F738">
-        <v>11462.39847</v>
+        <v>22548.71649</v>
       </c>
       <c r="G738">
-        <v>1687368</v>
+        <v>5268514</v>
       </c>
       <c r="H738">
-        <v>5753.04124</v>
+        <v>11531.10802</v>
       </c>
       <c r="I738">
-        <v>382921412.223849</v>
+        <v>748190390.432382</v>
       </c>
       <c r="J738">
-        <v>762676255.44706</v>
+        <v>1462864408.26157</v>
       </c>
       <c r="K738">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L738">
-        <v>0.439004341476988</v>
+        <v>0.444681389274536</v>
       </c>
       <c r="M738">
-        <v>1.14925228170872</v>
+        <v>1.20365383262339</v>
       </c>
       <c r="N738">
-        <v>0.866310784829582</v>
+        <v>0.847788327571202</v>
       </c>
       <c r="O738">
-        <v>1.22232209651148</v>
+        <v>1.24609904659423</v>
       </c>
       <c r="P738">
-        <v>1.29691683325285</v>
+        <v>1.31650044843657</v>
       </c>
       <c r="Q738">
-        <v>-1.05582986484397</v>
+        <v>-1.01632997227561</v>
       </c>
       <c r="R738">
-        <v>0.362655742904735</v>
+        <v>0.729345589923863</v>
       </c>
       <c r="S738">
-        <v>-1.63617601141703</v>
+        <v>-0.28303460992423</v>
       </c>
       <c r="T738">
-        <v>-1.65425330178106</v>
+        <v>-0.492890959199066</v>
       </c>
       <c r="U738">
-        <v>0.501905535308092</v>
+        <v>0.511386447433221</v>
       </c>
       <c r="V738">
-        <v>0.502075958821336</v>
+        <v>0.511455734521227</v>
       </c>
       <c r="W738">
-        <v>0.636979386366377</v>
+        <v>0.940356077218073</v>
       </c>
       <c r="X738">
-        <v>0.371813789292507</v>
+        <v>0.553880219660174</v>
       </c>
       <c r="Y738">
-        <v>-0.0391285589266773</v>
+        <v>0.142603376598697</v>
       </c>
       <c r="Z738">
-        <v>-0.325883091679455</v>
+        <v>-0.173648464701737</v>
       </c>
       <c r="AA738">
-        <v>-0.554064318431371</v>
+        <v>-0.413617885539902</v>
       </c>
       <c r="AB738">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AC738">
         <v>1</v>
       </c>
       <c r="AD738">
+        <v>3</v>
+      </c>
+      <c r="AE738">
+        <v>6</v>
+      </c>
+      <c r="AF738">
         <v>0</v>
       </c>
-      <c r="AE738">
-        <v>4</v>
-      </c>
-      <c r="AF738">
-        <v>12</v>
-      </c>
       <c r="AG738">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH738">
         <v>10</v>
+      </c>
+    </row>
+    <row r="739" spans="1:34">
+      <c r="A739" s="2">
+        <v>46082</v>
+      </c>
+      <c r="B739">
+        <v>66973.26</v>
+      </c>
+      <c r="C739">
+        <v>68199.99</v>
+      </c>
+      <c r="D739">
+        <v>65056</v>
+      </c>
+      <c r="E739">
+        <v>65776.47</v>
+      </c>
+      <c r="F739">
+        <v>23201.85859</v>
+      </c>
+      <c r="G739">
+        <v>5312013</v>
+      </c>
+      <c r="H739">
+        <v>11209.77201</v>
+      </c>
+      <c r="I739">
+        <v>747161922.848462</v>
+      </c>
+      <c r="J739">
+        <v>1545783742.9062</v>
+      </c>
+      <c r="K739">
+        <v>10</v>
+      </c>
+      <c r="L739">
+        <v>0.382551403062705</v>
+      </c>
+      <c r="M739">
+        <v>1.29850822150617</v>
+      </c>
+      <c r="N739">
+        <v>1.07765055795751</v>
+      </c>
+      <c r="O739">
+        <v>1.12500532136532</v>
+      </c>
+      <c r="P739">
+        <v>1.2337500940853</v>
+      </c>
+      <c r="Q739">
+        <v>-1.06547253915861</v>
+      </c>
+      <c r="R739">
+        <v>0.756367348154016</v>
+      </c>
+      <c r="S739">
+        <v>-0.215239807276917</v>
+      </c>
+      <c r="T739">
+        <v>-0.474323479807945</v>
+      </c>
+      <c r="U739">
+        <v>0.483141122790543</v>
+      </c>
+      <c r="V739">
+        <v>0.483354755331905</v>
+      </c>
+      <c r="W739">
+        <v>0.554472210027378</v>
+      </c>
+      <c r="X739">
+        <v>0.466445383839023</v>
+      </c>
+      <c r="Y739">
+        <v>-0.0678258912488755</v>
+      </c>
+      <c r="Z739">
+        <v>-0.356418748480079</v>
+      </c>
+      <c r="AA739">
+        <v>-0.435617814818945</v>
+      </c>
+      <c r="AB739">
+        <v>0.14</v>
+      </c>
+      <c r="AC739">
+        <v>1</v>
+      </c>
+      <c r="AD739">
+        <v>3</v>
+      </c>
+      <c r="AE739">
+        <v>6</v>
+      </c>
+      <c r="AF739">
+        <v>0</v>
+      </c>
+      <c r="AG739">
+        <v>1</v>
+      </c>
+      <c r="AH739">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="740" spans="1:34">
+      <c r="A740" s="2">
+        <v>46083</v>
+      </c>
+      <c r="B740">
+        <v>65776.48</v>
+      </c>
+      <c r="C740">
+        <v>70096</v>
+      </c>
+      <c r="D740">
+        <v>65259.21</v>
+      </c>
+      <c r="E740">
+        <v>68830.06</v>
+      </c>
+      <c r="F740">
+        <v>32010.38431</v>
+      </c>
+      <c r="G740">
+        <v>8397526</v>
+      </c>
+      <c r="H740">
+        <v>15335.91369</v>
+      </c>
+      <c r="I740">
+        <v>1037871544.54815</v>
+      </c>
+      <c r="J740">
+        <v>2164578841.84592</v>
+      </c>
+      <c r="K740">
+        <v>14</v>
+      </c>
+      <c r="L740">
+        <v>0.499934680572447</v>
+      </c>
+      <c r="M740">
+        <v>1.48448515995669</v>
+      </c>
+      <c r="N740">
+        <v>1.52197216229906</v>
+      </c>
+      <c r="O740">
+        <v>1.21082544584202</v>
+      </c>
+      <c r="P740">
+        <v>1.49731183354438</v>
+      </c>
+      <c r="Q740">
+        <v>-1.03782634886061</v>
+      </c>
+      <c r="R740">
+        <v>1.04714492697177</v>
+      </c>
+      <c r="S740">
+        <v>0.372694458400916</v>
+      </c>
+      <c r="T740">
+        <v>0.574061912093234</v>
+      </c>
+      <c r="U740">
+        <v>0.479091832871531</v>
+      </c>
+      <c r="V740">
+        <v>0.479479668046219</v>
+      </c>
+      <c r="W740">
+        <v>1.37793479433351</v>
+      </c>
+      <c r="X740">
+        <v>1.81008435005157</v>
+      </c>
+      <c r="Y740">
+        <v>1.22497434288705</v>
+      </c>
+      <c r="Z740">
+        <v>0.750801532507073</v>
+      </c>
+      <c r="AA740">
+        <v>-0.44145489215426</v>
+      </c>
+      <c r="AB740">
+        <v>0.1</v>
+      </c>
+      <c r="AC740">
+        <v>3</v>
+      </c>
+      <c r="AD740">
+        <v>6</v>
+      </c>
+      <c r="AE740">
+        <v>6</v>
+      </c>
+      <c r="AF740">
+        <v>0</v>
+      </c>
+      <c r="AG740">
+        <v>2</v>
+      </c>
+      <c r="AH740">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="741" spans="1:34">
+      <c r="A741" s="2">
+        <v>46084</v>
+      </c>
+      <c r="B741">
+        <v>68830.06</v>
+      </c>
+      <c r="C741">
+        <v>69258.08</v>
+      </c>
+      <c r="D741">
+        <v>66158</v>
+      </c>
+      <c r="E741">
+        <v>68338</v>
+      </c>
+      <c r="F741">
+        <v>24972.2418</v>
+      </c>
+      <c r="G741">
+        <v>7648119</v>
+      </c>
+      <c r="H741">
+        <v>12331.622</v>
+      </c>
+      <c r="I741">
+        <v>835461016.094694</v>
+      </c>
+      <c r="J741">
+        <v>1691848669.94302</v>
+      </c>
+      <c r="K741">
+        <v>10</v>
+      </c>
+      <c r="L741">
+        <v>0.522611178128871</v>
+      </c>
+      <c r="M741">
+        <v>1.64352353663198</v>
+      </c>
+      <c r="N741">
+        <v>1.81447029837044</v>
+      </c>
+      <c r="O741">
+        <v>1.18639169895096</v>
+      </c>
+      <c r="P741">
+        <v>1.64437062911388</v>
+      </c>
+      <c r="Q741">
+        <v>-0.978851427962898</v>
+      </c>
+      <c r="R741">
+        <v>0.830050351272977</v>
+      </c>
+      <c r="S741">
+        <v>-0.0497739414095012</v>
+      </c>
+      <c r="T741">
+        <v>0.317301011920919</v>
+      </c>
+      <c r="U741">
+        <v>0.493813174594521</v>
+      </c>
+      <c r="V741">
+        <v>0.493815452254859</v>
+      </c>
+      <c r="W741">
+        <v>0.912636145776068</v>
+      </c>
+      <c r="X741">
+        <v>1.76209210270624</v>
+      </c>
+      <c r="Y741">
+        <v>1.17038203041021</v>
+      </c>
+      <c r="Z741">
+        <v>0.767013582344305</v>
+      </c>
+      <c r="AA741">
+        <v>-0.487777638111406</v>
+      </c>
+      <c r="AB741">
+        <v>0.14</v>
+      </c>
+      <c r="AC741">
+        <v>7</v>
+      </c>
+      <c r="AD741">
+        <v>1</v>
+      </c>
+      <c r="AE741">
+        <v>6</v>
+      </c>
+      <c r="AF741">
+        <v>0</v>
+      </c>
+      <c r="AG741">
+        <v>2</v>
+      </c>
+      <c r="AH741">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="742" spans="1:34">
+      <c r="A742" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B742">
+        <v>68338.01</v>
+      </c>
+      <c r="C742">
+        <v>74050</v>
+      </c>
+      <c r="D742">
+        <v>67400</v>
+      </c>
+      <c r="E742">
+        <v>72666.77</v>
+      </c>
+      <c r="F742">
+        <v>44919.0761</v>
+      </c>
+      <c r="G742">
+        <v>8618302</v>
+      </c>
+      <c r="H742">
+        <v>23641.35243</v>
+      </c>
+      <c r="I742">
+        <v>1685099057.93018</v>
+      </c>
+      <c r="J742">
+        <v>3202864447.63246</v>
+      </c>
+      <c r="K742">
+        <v>22</v>
+      </c>
+      <c r="L742">
+        <v>0.642733106798037</v>
+      </c>
+      <c r="M742">
+        <v>2.31014355371997</v>
+      </c>
+      <c r="N742">
+        <v>2.20391672956938</v>
+      </c>
+      <c r="O742">
+        <v>1.37947045207221</v>
+      </c>
+      <c r="P742">
+        <v>2.4892769893522</v>
+      </c>
+      <c r="Q742">
+        <v>-0.650331370305316</v>
+      </c>
+      <c r="R742">
+        <v>1.46144835176653</v>
+      </c>
+      <c r="S742">
+        <v>0.972645178920609</v>
+      </c>
+      <c r="T742">
+        <v>0.635843787094275</v>
+      </c>
+      <c r="U742">
+        <v>0.526309855023933</v>
+      </c>
+      <c r="V742">
+        <v>0.526122502366841</v>
+      </c>
+      <c r="W742">
+        <v>2.05647400771588</v>
+      </c>
+      <c r="X742">
+        <v>2.89702941156902</v>
+      </c>
+      <c r="Y742">
+        <v>2.63452237985512</v>
+      </c>
+      <c r="Z742">
+        <v>2.33211795808063</v>
+      </c>
+      <c r="AA742">
+        <v>-0.291197834546469</v>
+      </c>
+      <c r="AB742">
+        <v>0.1</v>
+      </c>
+      <c r="AC742">
+        <v>3</v>
+      </c>
+      <c r="AD742">
+        <v>6</v>
+      </c>
+      <c r="AE742">
+        <v>0</v>
+      </c>
+      <c r="AF742">
+        <v>10</v>
+      </c>
+      <c r="AG742">
+        <v>2</v>
+      </c>
+      <c r="AH742">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="743" spans="1:34">
+      <c r="A743" s="2">
+        <v>46086</v>
+      </c>
+      <c r="B743">
+        <v>72666.77</v>
+      </c>
+      <c r="C743">
+        <v>73558.15</v>
+      </c>
+      <c r="D743">
+        <v>70645.47</v>
+      </c>
+      <c r="E743">
+        <v>70890.72</v>
+      </c>
+      <c r="F743">
+        <v>26590.51253</v>
+      </c>
+      <c r="G743">
+        <v>6709160</v>
+      </c>
+      <c r="H743">
+        <v>12299.51467</v>
+      </c>
+      <c r="I743">
+        <v>886773462.472777</v>
+      </c>
+      <c r="J743">
+        <v>1917514690.38783</v>
+      </c>
+      <c r="K743">
+        <v>18</v>
+      </c>
+      <c r="L743">
+        <v>0.584601341001089</v>
+      </c>
+      <c r="M743">
+        <v>2.97683891380703</v>
+      </c>
+      <c r="N743">
+        <v>2.27043350224874</v>
+      </c>
+      <c r="O743">
+        <v>1.3219110041489</v>
+      </c>
+      <c r="P743">
+        <v>2.73030340700501</v>
+      </c>
+      <c r="Q743">
+        <v>-0.540246367966655</v>
+      </c>
+      <c r="R743">
+        <v>0.88009498284861</v>
+      </c>
+      <c r="S743">
+        <v>0.0583682453570767</v>
+      </c>
+      <c r="T743">
+        <v>0.0316229692041319</v>
+      </c>
+      <c r="U743">
+        <v>0.462552749072565</v>
+      </c>
+      <c r="V743">
+        <v>0.462459801178066</v>
+      </c>
+      <c r="W743">
+        <v>1.1631118835081</v>
+      </c>
+      <c r="X743">
+        <v>2.29787415230646</v>
+      </c>
+      <c r="Y743">
+        <v>2.02528540669919</v>
+      </c>
+      <c r="Z743">
+        <v>1.90592001512494</v>
+      </c>
+      <c r="AA743">
+        <v>-0.341589271594018</v>
+      </c>
+      <c r="AB743">
+        <v>0.22</v>
+      </c>
+      <c r="AC743">
+        <v>7</v>
+      </c>
+      <c r="AD743">
+        <v>1</v>
+      </c>
+      <c r="AE743">
+        <v>0</v>
+      </c>
+      <c r="AF743">
+        <v>2</v>
+      </c>
+      <c r="AG743">
+        <v>11</v>
+      </c>
+      <c r="AH743">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="744" spans="1:34">
+      <c r="A744" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B744">
+        <v>70891.02</v>
+      </c>
+      <c r="C744">
+        <v>71419.98</v>
+      </c>
+      <c r="D744">
+        <v>67744.78</v>
+      </c>
+      <c r="E744">
+        <v>68114.02</v>
+      </c>
+      <c r="F744">
+        <v>22629.88722</v>
+      </c>
+      <c r="G744">
+        <v>5302899</v>
+      </c>
+      <c r="H744">
+        <v>10464.09351</v>
+      </c>
+      <c r="I744">
+        <v>728091757.782213</v>
+      </c>
+      <c r="J744">
+        <v>1574601198.87489</v>
+      </c>
+      <c r="K744">
+        <v>12</v>
+      </c>
+      <c r="L744">
+        <v>0.501900511911101</v>
+      </c>
+      <c r="M744">
+        <v>3.46707805582067</v>
+      </c>
+      <c r="N744">
+        <v>2.09735679993193</v>
+      </c>
+      <c r="O744">
+        <v>1.06461735978486</v>
+      </c>
+      <c r="P744">
+        <v>2.15732307428671</v>
+      </c>
+      <c r="Q744">
+        <v>-0.509262039648984</v>
+      </c>
+      <c r="R744">
+        <v>0.762885168697835</v>
+      </c>
+      <c r="S744">
+        <v>-0.204301974768272</v>
+      </c>
+      <c r="T744">
+        <v>-0.412914719814512</v>
+      </c>
+      <c r="U744">
+        <v>0.462401487390179</v>
+      </c>
+      <c r="V744">
+        <v>0.462397563460806</v>
+      </c>
+      <c r="W744">
+        <v>0.039144207579585</v>
+      </c>
+      <c r="X744">
+        <v>1.54292748101866</v>
+      </c>
+      <c r="Y744">
+        <v>1.08503312243931</v>
+      </c>
+      <c r="Z744">
+        <v>0.98136810203268</v>
+      </c>
+      <c r="AA744">
+        <v>-0.190175696503598</v>
+      </c>
+      <c r="AB744">
+        <v>0.18</v>
+      </c>
+      <c r="AC744">
+        <v>7</v>
+      </c>
+      <c r="AD744">
+        <v>1</v>
+      </c>
+      <c r="AE744">
+        <v>11</v>
+      </c>
+      <c r="AF744">
+        <v>2</v>
+      </c>
+      <c r="AG744">
+        <v>11</v>
+      </c>
+      <c r="AH744">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="745" spans="1:34">
+      <c r="A745" s="2">
+        <v>46088</v>
+      </c>
+      <c r="B745">
+        <v>68114.02</v>
+      </c>
+      <c r="C745">
+        <v>68551.04</v>
+      </c>
+      <c r="D745">
+        <v>66915.26</v>
+      </c>
+      <c r="E745">
+        <v>67262.91</v>
+      </c>
+      <c r="F745">
+        <v>12719.54315</v>
+      </c>
+      <c r="G745">
+        <v>2067476</v>
+      </c>
+      <c r="H745">
+        <v>5910.76849</v>
+      </c>
+      <c r="I745">
+        <v>400477518.356691</v>
+      </c>
+      <c r="J745">
+        <v>861729861.853049</v>
+      </c>
+      <c r="K745">
+        <v>12</v>
+      </c>
+      <c r="L745">
+        <v>0.486041024532652</v>
+      </c>
+      <c r="M745">
+        <v>3.69914269352909</v>
+      </c>
+      <c r="N745">
+        <v>1.89771759974879</v>
+      </c>
+      <c r="O745">
+        <v>0.806385918660272</v>
+      </c>
+      <c r="P745">
+        <v>1.55860290513904</v>
+      </c>
+      <c r="Q745">
+        <v>-0.471427449445413</v>
+      </c>
+      <c r="R745">
+        <v>0.441522601385245</v>
+      </c>
+      <c r="S745">
+        <v>-1.17924724936164</v>
+      </c>
+      <c r="T745">
+        <v>-1.44283202989079</v>
+      </c>
+      <c r="U745">
+        <v>0.464699747490538</v>
+      </c>
+      <c r="V745">
+        <v>0.464736730250372</v>
+      </c>
+      <c r="W745">
+        <v>-0.333980010772003</v>
+      </c>
+      <c r="X745">
+        <v>1.35042429732525</v>
+      </c>
+      <c r="Y745">
+        <v>0.821925700409095</v>
+      </c>
+      <c r="Z745">
+        <v>0.724401348402699</v>
+      </c>
+      <c r="AA745">
+        <v>-0.436510145805049</v>
+      </c>
+      <c r="AB745">
+        <v>0.12</v>
+      </c>
+      <c r="AC745">
+        <v>7</v>
+      </c>
+      <c r="AD745">
+        <v>1</v>
+      </c>
+      <c r="AE745">
+        <v>6</v>
+      </c>
+      <c r="AF745">
+        <v>2</v>
+      </c>
+      <c r="AG745">
+        <v>11</v>
+      </c>
+      <c r="AH745">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="746" spans="1:34">
+      <c r="A746" s="2">
+        <v>46089</v>
+      </c>
+      <c r="B746">
+        <v>67262.91</v>
+      </c>
+      <c r="C746">
+        <v>68200</v>
+      </c>
+      <c r="D746">
+        <v>65618.49</v>
+      </c>
+      <c r="E746">
+        <v>65971.2</v>
+      </c>
+      <c r="F746">
+        <v>21593.63901</v>
+      </c>
+      <c r="G746">
+        <v>3028392</v>
+      </c>
+      <c r="H746">
+        <v>11268.64926</v>
+      </c>
+      <c r="I746">
+        <v>755732359.169672</v>
+      </c>
+      <c r="J746">
+        <v>1447522160.31545</v>
+      </c>
+      <c r="K746">
+        <v>8</v>
+      </c>
+      <c r="L746">
+        <v>0.468447889771018</v>
+      </c>
+      <c r="M746">
+        <v>4.08389169144137</v>
+      </c>
+      <c r="N746">
+        <v>1.67591237083055</v>
+      </c>
+      <c r="O746">
+        <v>0.520975312853134</v>
+      </c>
+      <c r="P746">
+        <v>0.874510756420085</v>
+      </c>
+      <c r="Q746">
+        <v>-0.400860760726905</v>
+      </c>
+      <c r="R746">
+        <v>0.831008602700381</v>
+      </c>
+      <c r="S746">
+        <v>-0.142636611683186</v>
+      </c>
+      <c r="T746">
+        <v>-1.17932732544757</v>
+      </c>
+      <c r="U746">
+        <v>0.521850404870689</v>
+      </c>
+      <c r="V746">
+        <v>0.522086901249912</v>
+      </c>
+      <c r="W746">
+        <v>-1.42436656258023</v>
+      </c>
+      <c r="X746">
+        <v>1.11624688019134</v>
+      </c>
+      <c r="Y746">
+        <v>0.378661972669408</v>
+      </c>
+      <c r="Z746">
+        <v>0.196045037517012</v>
+      </c>
+      <c r="AA746">
+        <v>-0.443269289769076</v>
+      </c>
+      <c r="AB746">
+        <v>0.12</v>
+      </c>
+      <c r="AC746">
+        <v>7</v>
+      </c>
+      <c r="AD746">
+        <v>1</v>
+      </c>
+      <c r="AE746">
+        <v>11</v>
+      </c>
+      <c r="AF746">
+        <v>2</v>
+      </c>
+      <c r="AG746">
+        <v>11</v>
+      </c>
+      <c r="AH746">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="747" spans="1:34">
+      <c r="A747" s="2">
+        <v>46090</v>
+      </c>
+      <c r="B747">
+        <v>65971.2</v>
+      </c>
+      <c r="C747">
+        <v>69516.65</v>
+      </c>
+      <c r="D747">
+        <v>65821.97</v>
+      </c>
+      <c r="E747">
+        <v>68432.16</v>
+      </c>
+      <c r="F747">
+        <v>28896.7213</v>
+      </c>
+      <c r="G747">
+        <v>5093667</v>
+      </c>
+      <c r="H747">
+        <v>14101.45378</v>
+      </c>
+      <c r="I747">
+        <v>960195772.915906</v>
+      </c>
+      <c r="J747">
+        <v>1967622051.44968</v>
+      </c>
+      <c r="K747">
+        <v>13</v>
+      </c>
+      <c r="L747">
+        <v>0.572694685938258</v>
+      </c>
+      <c r="M747">
+        <v>4.24709899001734</v>
+      </c>
+      <c r="N747">
+        <v>1.62234812551893</v>
+      </c>
+      <c r="O747">
+        <v>0.471348413343718</v>
+      </c>
+      <c r="P747">
+        <v>0.957101452382577</v>
+      </c>
+      <c r="Q747">
+        <v>-0.420162887358696</v>
+      </c>
+      <c r="R747">
+        <v>1.21092020555871</v>
+      </c>
+      <c r="S747">
+        <v>0.653973523330309</v>
+      </c>
+      <c r="T747">
+        <v>-0.225882349354089</v>
+      </c>
+      <c r="U747">
+        <v>0.487994940104156</v>
+      </c>
+      <c r="V747">
+        <v>0.487998074736185</v>
+      </c>
+      <c r="W747">
+        <v>-0.047916505213054</v>
+      </c>
+      <c r="X747">
+        <v>1.82798304907499</v>
+      </c>
+      <c r="Y747">
+        <v>1.41077971880454</v>
+      </c>
+      <c r="Z747">
+        <v>1.35145410765773</v>
+      </c>
+      <c r="AA747">
+        <v>-0.488377317380244</v>
+      </c>
+      <c r="AB747">
+        <v>0.08</v>
+      </c>
+      <c r="AC747">
+        <v>7</v>
+      </c>
+      <c r="AD747">
+        <v>1</v>
+      </c>
+      <c r="AE747">
+        <v>11</v>
+      </c>
+      <c r="AF747">
+        <v>2</v>
+      </c>
+      <c r="AG747">
+        <v>11</v>
+      </c>
+      <c r="AH747">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="748" spans="1:34">
+      <c r="A748" s="2">
+        <v>46091</v>
+      </c>
+      <c r="B748">
+        <v>68432.16</v>
+      </c>
+      <c r="C748">
+        <v>71777</v>
+      </c>
+      <c r="D748">
+        <v>68391.41</v>
+      </c>
+      <c r="E748">
+        <v>69948.63</v>
+      </c>
+      <c r="F748">
+        <v>32602.57726</v>
+      </c>
+      <c r="G748">
+        <v>5176064</v>
+      </c>
+      <c r="H748">
+        <v>16453.82839</v>
+      </c>
+      <c r="I748">
+        <v>1157238967.10045</v>
+      </c>
+      <c r="J748">
+        <v>2292525621.44052</v>
+      </c>
+      <c r="K748">
+        <v>15</v>
+      </c>
+      <c r="L748">
+        <v>0.609524305348962</v>
+      </c>
+      <c r="M748">
+        <v>4.31869133777328</v>
+      </c>
+      <c r="N748">
+        <v>1.6358714490152</v>
+      </c>
+      <c r="O748">
+        <v>0.535399998332295</v>
+      </c>
+      <c r="P748">
+        <v>1.4829929972817</v>
+      </c>
+      <c r="Q748">
+        <v>-0.482454900899036</v>
+      </c>
+      <c r="R748">
+        <v>1.38882061511487</v>
+      </c>
+      <c r="S748">
+        <v>1.01708190667839</v>
+      </c>
+      <c r="T748">
+        <v>-0.148442291932274</v>
+      </c>
+      <c r="U748">
+        <v>0.504678763853039</v>
+      </c>
+      <c r="V748">
+        <v>0.50478780096394</v>
+      </c>
+      <c r="W748">
+        <v>0.66140864982948</v>
+      </c>
+      <c r="X748">
+        <v>2.13267300213708</v>
+      </c>
+      <c r="Y748">
+        <v>1.91307081593755</v>
+      </c>
+      <c r="Z748">
+        <v>1.90666517827077</v>
+      </c>
+      <c r="AA748">
+        <v>-0.547963031154319</v>
+      </c>
+      <c r="AB748">
+        <v>0.13</v>
+      </c>
+      <c r="AC748">
+        <v>3</v>
+      </c>
+      <c r="AD748">
+        <v>6</v>
+      </c>
+      <c r="AE748">
+        <v>0</v>
+      </c>
+      <c r="AF748">
+        <v>10</v>
+      </c>
+      <c r="AG748">
+        <v>2</v>
+      </c>
+      <c r="AH748">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="749" spans="1:34">
+      <c r="A749" s="2">
+        <v>46092</v>
+      </c>
+      <c r="B749">
+        <v>69948.64</v>
+      </c>
+      <c r="C749">
+        <v>71321</v>
+      </c>
+      <c r="D749">
+        <v>68977.91</v>
+      </c>
+      <c r="E749">
+        <v>70191.86</v>
+      </c>
+      <c r="F749">
+        <v>27249.27542</v>
+      </c>
+      <c r="G749">
+        <v>4759855</v>
+      </c>
+      <c r="H749">
+        <v>14015.31615</v>
+      </c>
+      <c r="I749">
+        <v>982971805.599723</v>
+      </c>
+      <c r="J749">
+        <v>1911300596.23417</v>
+      </c>
+      <c r="K749">
+        <v>18</v>
+      </c>
+      <c r="L749">
+        <v>0.547486828008657</v>
+      </c>
+      <c r="M749">
+        <v>4.4790300947325</v>
+      </c>
+      <c r="N749">
+        <v>1.63549409872723</v>
+      </c>
+      <c r="O749">
+        <v>0.566687315396433</v>
+      </c>
+      <c r="P749">
+        <v>2.0588992319175</v>
+      </c>
+      <c r="Q749">
+        <v>-0.393781381192645</v>
+      </c>
+      <c r="R749">
+        <v>1.15124968682382</v>
+      </c>
+      <c r="S749">
+        <v>0.529538664228612</v>
+      </c>
+      <c r="T749">
+        <v>-0.371521639707146</v>
+      </c>
+      <c r="U749">
+        <v>0.514337204713827</v>
+      </c>
+      <c r="V749">
+        <v>0.51429472032629</v>
+      </c>
+      <c r="W749">
+        <v>0.968556242521303</v>
+      </c>
+      <c r="X749">
+        <v>2.06008031343354</v>
+      </c>
+      <c r="Y749">
+        <v>1.86199931476493</v>
+      </c>
+      <c r="Z749">
+        <v>1.88392609898938</v>
+      </c>
+      <c r="AA749">
+        <v>-0.741979144676498</v>
+      </c>
+      <c r="AB749">
+        <v>0.15</v>
+      </c>
+      <c r="AC749">
+        <v>7</v>
+      </c>
+      <c r="AD749">
+        <v>1</v>
+      </c>
+      <c r="AE749">
+        <v>11</v>
+      </c>
+      <c r="AF749">
+        <v>2</v>
+      </c>
+      <c r="AG749">
+        <v>11</v>
+      </c>
+      <c r="AH749">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="750" spans="1:34">
+      <c r="A750" s="2">
+        <v>46093</v>
+      </c>
+      <c r="B750">
+        <v>70191.86</v>
+      </c>
+      <c r="C750">
+        <v>70800</v>
+      </c>
+      <c r="D750">
+        <v>69205.91</v>
+      </c>
+      <c r="E750">
+        <v>70541.34</v>
+      </c>
+      <c r="F750">
+        <v>21997.1605</v>
+      </c>
+      <c r="G750">
+        <v>4344059</v>
+      </c>
+      <c r="H750">
+        <v>10545.03396</v>
+      </c>
+      <c r="I750">
+        <v>738758111.898918</v>
+      </c>
+      <c r="J750">
+        <v>1540745224.51011</v>
+      </c>
+      <c r="K750">
+        <v>15</v>
+      </c>
+      <c r="L750">
+        <v>0.566290807056999</v>
+      </c>
+      <c r="M750">
+        <v>4.61896235100638</v>
+      </c>
+      <c r="N750">
+        <v>1.62900566566908</v>
+      </c>
+      <c r="O750">
+        <v>0.576166933029449</v>
+      </c>
+      <c r="P750">
+        <v>2.71039439005161</v>
+      </c>
+      <c r="Q750">
+        <v>-0.298651459404012</v>
+      </c>
+      <c r="R750">
+        <v>0.93881460673856</v>
+      </c>
+      <c r="S750">
+        <v>0.00237970432363577</v>
+      </c>
+      <c r="T750">
+        <v>-0.556100020639567</v>
+      </c>
+      <c r="U750">
+        <v>0.479381598365844</v>
+      </c>
+      <c r="V750">
+        <v>0.479481033039587</v>
+      </c>
+      <c r="W750">
+        <v>1.14400184575922</v>
+      </c>
+      <c r="X750">
+        <v>1.99990513791892</v>
+      </c>
+      <c r="Y750">
+        <v>1.85850709203275</v>
+      </c>
+      <c r="Z750">
+        <v>1.88750500007607</v>
+      </c>
+      <c r="AA750">
+        <v>-1.11311657795011</v>
+      </c>
+      <c r="AB750">
+        <v>0.18</v>
+      </c>
+      <c r="AC750">
+        <v>7</v>
+      </c>
+      <c r="AD750">
+        <v>1</v>
+      </c>
+      <c r="AE750">
+        <v>6</v>
+      </c>
+      <c r="AF750">
+        <v>2</v>
+      </c>
+      <c r="AG750">
+        <v>11</v>
+      </c>
+      <c r="AH750">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="751" spans="1:34">
+      <c r="A751" s="2">
+        <v>46094</v>
+      </c>
+      <c r="B751">
+        <v>70541.34</v>
+      </c>
+      <c r="C751">
+        <v>73913.74</v>
+      </c>
+      <c r="D751">
+        <v>70386.01</v>
+      </c>
+      <c r="E751">
+        <v>70930</v>
+      </c>
+      <c r="F751">
+        <v>35996.61678</v>
+      </c>
+      <c r="G751">
+        <v>5312490</v>
+      </c>
+      <c r="H751">
+        <v>18310.3426</v>
+      </c>
+      <c r="I751">
+        <v>1319530652.95863</v>
+      </c>
+      <c r="J751">
+        <v>2591768526.29615</v>
+      </c>
+      <c r="K751">
+        <v>16</v>
+      </c>
+      <c r="L751">
+        <v>0.615864760381074</v>
+      </c>
+      <c r="M751">
+        <v>4.65033861253862</v>
+      </c>
+      <c r="N751">
+        <v>1.62100055369002</v>
+      </c>
+      <c r="O751">
+        <v>0.569420817664776</v>
+      </c>
+      <c r="P751">
+        <v>3.43922634511074</v>
+      </c>
+      <c r="Q751">
+        <v>-0.287921472024303</v>
+      </c>
+      <c r="R751">
+        <v>1.50289339595402</v>
+      </c>
+      <c r="S751">
+        <v>1.20135420024001</v>
+      </c>
+      <c r="T751">
+        <v>-0.0448797305401199</v>
+      </c>
+      <c r="U751">
+        <v>0.508668431589198</v>
+      </c>
+      <c r="V751">
+        <v>0.509123650345561</v>
+      </c>
+      <c r="W751">
+        <v>1.06178313599411</v>
+      </c>
+      <c r="X751">
+        <v>1.96122496878805</v>
+      </c>
+      <c r="Y751">
+        <v>1.8672558137675</v>
+      </c>
+      <c r="Z751">
+        <v>1.88607034980139</v>
+      </c>
+      <c r="AA751">
+        <v>-1.00138631563804</v>
+      </c>
+      <c r="AB751">
+        <v>0.15</v>
+      </c>
+      <c r="AC751">
+        <v>3</v>
+      </c>
+      <c r="AD751">
+        <v>6</v>
+      </c>
+      <c r="AE751">
+        <v>0</v>
+      </c>
+      <c r="AF751">
+        <v>10</v>
+      </c>
+      <c r="AG751">
+        <v>2</v>
+      </c>
+      <c r="AH751">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="752" spans="1:34">
+      <c r="A752" s="2">
+        <v>46095</v>
+      </c>
+      <c r="B752">
+        <v>70930.01</v>
+      </c>
+      <c r="C752">
+        <v>71307.92</v>
+      </c>
+      <c r="D752">
+        <v>70317</v>
+      </c>
+      <c r="E752">
+        <v>71211.95</v>
+      </c>
+      <c r="F752">
+        <v>13017.24737</v>
+      </c>
+      <c r="G752">
+        <v>1661739</v>
+      </c>
+      <c r="H752">
+        <v>6242.10104</v>
+      </c>
+      <c r="I752">
+        <v>441895405.358563</v>
+      </c>
+      <c r="J752">
+        <v>921308630.946277</v>
+      </c>
+      <c r="K752">
+        <v>15</v>
+      </c>
+      <c r="L752">
+        <v>0.600885015991885</v>
+      </c>
+      <c r="M752">
+        <v>4.66911160752891</v>
+      </c>
+      <c r="N752">
+        <v>1.61073981405444</v>
+      </c>
+      <c r="O752">
+        <v>0.533828080715911</v>
+      </c>
+      <c r="P752">
+        <v>4.18379447667998</v>
+      </c>
+      <c r="Q752">
+        <v>-0.221766482926462</v>
+      </c>
+      <c r="R752">
+        <v>0.555623570379379</v>
+      </c>
+      <c r="S752">
+        <v>-1.27777554633895</v>
+      </c>
+      <c r="T752">
+        <v>-1.8382317458546</v>
+      </c>
+      <c r="U752">
+        <v>0.479525422124632</v>
+      </c>
+      <c r="V752">
+        <v>0.479638842528471</v>
+      </c>
+      <c r="W752">
+        <v>0.831978732171985</v>
+      </c>
+      <c r="X752">
+        <v>1.91775066050784</v>
+      </c>
+      <c r="Y752">
+        <v>1.85373268638769</v>
+      </c>
+      <c r="Z752">
+        <v>1.85469862094928</v>
+      </c>
+      <c r="AA752">
+        <v>-1.58108788645377</v>
+      </c>
+      <c r="AB752">
+        <v>0.16</v>
+      </c>
+      <c r="AC752">
+        <v>7</v>
+      </c>
+      <c r="AD752">
+        <v>1</v>
+      </c>
+      <c r="AE752">
+        <v>6</v>
+      </c>
+      <c r="AF752">
+        <v>0</v>
+      </c>
+      <c r="AG752">
+        <v>11</v>
+      </c>
+      <c r="AH752">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="753" spans="1:34">
+      <c r="A753" s="2">
+        <v>46096</v>
+      </c>
+      <c r="B753">
+        <v>71211.95</v>
+      </c>
+      <c r="C753">
+        <v>73199</v>
+      </c>
+      <c r="D753">
+        <v>70858.82</v>
+      </c>
+      <c r="E753">
+        <v>72815.24</v>
+      </c>
+      <c r="F753">
+        <v>14037.30704</v>
+      </c>
+      <c r="G753">
+        <v>2509013</v>
+      </c>
+      <c r="H753">
+        <v>7307.01776</v>
+      </c>
+      <c r="I753">
+        <v>524440519.762776</v>
+      </c>
+      <c r="J753">
+        <v>1007334955.24365</v>
+      </c>
+      <c r="K753">
+        <v>23</v>
+      </c>
+      <c r="L753">
+        <v>0.664349494233454</v>
+      </c>
+      <c r="M753">
+        <v>4.4439736500024</v>
+      </c>
+      <c r="N753">
+        <v>1.65427873580991</v>
+      </c>
+      <c r="O753">
+        <v>0.704427806759467</v>
+      </c>
+      <c r="P753">
+        <v>5.16145960018193</v>
+      </c>
+      <c r="Q753">
+        <v>-0.207739313536742</v>
+      </c>
+      <c r="R753">
+        <v>0.608017035679143</v>
+      </c>
+      <c r="S753">
+        <v>-1.02730056415042</v>
+      </c>
+      <c r="T753">
+        <v>-1.3012643189034</v>
+      </c>
+      <c r="U753">
+        <v>0.520542703752101</v>
+      </c>
+      <c r="V753">
+        <v>0.520621782290804</v>
+      </c>
+      <c r="W753">
+        <v>1.11360342585445</v>
+      </c>
+      <c r="X753">
+        <v>2.11565910891708</v>
+      </c>
+      <c r="Y753">
+        <v>2.19049499682007</v>
+      </c>
+      <c r="Z753">
+        <v>2.19755318577302</v>
+      </c>
+      <c r="AA753">
+        <v>-1.86109395986771</v>
+      </c>
+      <c r="AB753">
+        <v>0.15</v>
+      </c>
+      <c r="AC753">
+        <v>7</v>
+      </c>
+      <c r="AD753">
+        <v>1</v>
+      </c>
+      <c r="AE753">
+        <v>6</v>
+      </c>
+      <c r="AF753">
+        <v>0</v>
+      </c>
+      <c r="AG753">
+        <v>11</v>
+      </c>
+      <c r="AH753">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="754" spans="1:34">
+      <c r="A754" s="2">
+        <v>46097</v>
+      </c>
+      <c r="B754">
+        <v>72815.25</v>
+      </c>
+      <c r="C754">
+        <v>74909.08</v>
+      </c>
+      <c r="D754">
+        <v>72270.41</v>
+      </c>
+      <c r="E754">
+        <v>74884.67</v>
+      </c>
+      <c r="F754">
+        <v>28409.53019</v>
+      </c>
+      <c r="G754">
+        <v>5396482</v>
+      </c>
+      <c r="H754">
+        <v>15204.22255</v>
+      </c>
+      <c r="I754">
+        <v>1122045159.19948</v>
+      </c>
+      <c r="J754">
+        <v>2095859511.56486</v>
+      </c>
+      <c r="K754">
+        <v>28</v>
+      </c>
+      <c r="L754">
+        <v>0.648180335949274</v>
+      </c>
+      <c r="M754">
+        <v>4.07490131653378</v>
+      </c>
+      <c r="N754">
+        <v>1.7423644177895</v>
+      </c>
+      <c r="O754">
+        <v>1.14624758895295</v>
+      </c>
+      <c r="P754">
+        <v>0.380726341893493</v>
+      </c>
+      <c r="Q754">
+        <v>0.43811913262824</v>
+      </c>
+      <c r="R754">
+        <v>1.2162032961522</v>
+      </c>
+      <c r="S754">
+        <v>0.654125905642059</v>
+      </c>
+      <c r="T754">
+        <v>0.181639367831738</v>
+      </c>
+      <c r="U754">
+        <v>0.535180358433094</v>
+      </c>
+      <c r="V754">
+        <v>0.535362772651547</v>
+      </c>
+      <c r="W754">
+        <v>1.61935878642993</v>
+      </c>
+      <c r="X754">
+        <v>2.29061569073182</v>
+      </c>
+      <c r="Y754">
+        <v>2.47012078788179</v>
+      </c>
+      <c r="Z754">
+        <v>2.48805851087557</v>
+      </c>
+      <c r="AA754">
+        <v>-2.0115848959717</v>
+      </c>
+      <c r="AB754">
+        <v>0.23</v>
+      </c>
+      <c r="AC754">
+        <v>3</v>
+      </c>
+      <c r="AD754">
+        <v>6</v>
+      </c>
+      <c r="AE754">
+        <v>0</v>
+      </c>
+      <c r="AF754">
+        <v>10</v>
+      </c>
+      <c r="AG754">
+        <v>2</v>
+      </c>
+      <c r="AH754">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="755" spans="1:34">
+      <c r="A755" s="2">
+        <v>46098</v>
+      </c>
+      <c r="B755">
+        <v>74884.67</v>
+      </c>
+      <c r="C755">
+        <v>76000</v>
+      </c>
+      <c r="D755">
+        <v>73399.19</v>
+      </c>
+      <c r="E755">
+        <v>73909.36</v>
+      </c>
+      <c r="F755">
+        <v>24521.26636</v>
+      </c>
+      <c r="G755">
+        <v>4863187</v>
+      </c>
+      <c r="H755">
+        <v>11791.2523</v>
+      </c>
+      <c r="I755">
+        <v>878396858.780886</v>
+      </c>
+      <c r="J755">
+        <v>1825976731.33267</v>
+      </c>
+      <c r="K755">
+        <v>26</v>
+      </c>
+      <c r="L755">
+        <v>0.633202506369207</v>
+      </c>
+      <c r="M755">
+        <v>4.08011713996269</v>
+      </c>
+      <c r="N755">
+        <v>1.73086868183875</v>
+      </c>
+      <c r="O755">
+        <v>1.06132112911045</v>
+      </c>
+      <c r="P755">
+        <v>0.106668124208705</v>
+      </c>
+      <c r="Q755">
+        <v>0.859626472596602</v>
+      </c>
+      <c r="R755">
+        <v>1.04023807018543</v>
+      </c>
+      <c r="S755">
+        <v>0.275166061440749</v>
+      </c>
+      <c r="T755">
+        <v>-0.10971052024193</v>
+      </c>
+      <c r="U755">
+        <v>0.480858212087869</v>
+      </c>
+      <c r="V755">
+        <v>0.48105588845034</v>
+      </c>
+      <c r="W755">
+        <v>0.740874011403525</v>
+      </c>
+      <c r="X755">
+        <v>1.93423577788504</v>
+      </c>
+      <c r="Y755">
+        <v>1.99789496640278</v>
+      </c>
+      <c r="Z755">
+        <v>2.00628767270374</v>
+      </c>
+      <c r="AA755">
+        <v>-1.83442300505666</v>
+      </c>
+      <c r="AB755">
+        <v>0.28</v>
+      </c>
+      <c r="AC755">
+        <v>7</v>
+      </c>
+      <c r="AD755">
+        <v>1</v>
+      </c>
+      <c r="AE755">
+        <v>11</v>
+      </c>
+      <c r="AF755">
+        <v>2</v>
+      </c>
+      <c r="AG755">
+        <v>11</v>
+      </c>
+      <c r="AH755">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="756" spans="1:34">
+      <c r="A756" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B756">
+        <v>73909.37</v>
+      </c>
+      <c r="C756">
+        <v>74672.34</v>
+      </c>
+      <c r="D756">
+        <v>70500</v>
+      </c>
+      <c r="E756">
+        <v>71246.54</v>
+      </c>
+      <c r="F756">
+        <v>23392.88093</v>
+      </c>
+      <c r="G756">
+        <v>4733897</v>
+      </c>
+      <c r="H756">
+        <v>11709.17057</v>
+      </c>
+      <c r="I756">
+        <v>847905482.697256</v>
+      </c>
+      <c r="J756">
+        <v>1692949838.97774</v>
+      </c>
+      <c r="K756">
+        <v>23</v>
+      </c>
+      <c r="L756">
+        <v>0.463105485118072</v>
+      </c>
+      <c r="M756">
+        <v>3.98769698353448</v>
+      </c>
+      <c r="N756">
+        <v>1.58835584630223</v>
+      </c>
+      <c r="O756">
+        <v>0.13607474806784</v>
+      </c>
+      <c r="P756">
+        <v>0.00677948879560918</v>
+      </c>
+      <c r="Q756">
+        <v>1.06409088323671</v>
+      </c>
+      <c r="R756">
+        <v>0.990824685462919</v>
+      </c>
+      <c r="S756">
+        <v>0.157312430636378</v>
+      </c>
+      <c r="T756">
+        <v>-0.178655479452952</v>
+      </c>
+      <c r="U756">
+        <v>0.500544187141297</v>
+      </c>
+      <c r="V756">
+        <v>0.500845012164832</v>
+      </c>
+      <c r="W756">
+        <v>-0.757990258921783</v>
+      </c>
+      <c r="X756">
+        <v>1.39770716715841</v>
+      </c>
+      <c r="Y756">
+        <v>1.25128229320912</v>
+      </c>
+      <c r="Z756">
+        <v>1.23675829339515</v>
+      </c>
+      <c r="AA756">
+        <v>-1.0538008342955</v>
+      </c>
+      <c r="AB756">
+        <v>0.26</v>
+      </c>
+      <c r="AC756">
+        <v>7</v>
+      </c>
+      <c r="AD756">
+        <v>1</v>
+      </c>
+      <c r="AE756">
+        <v>11</v>
+      </c>
+      <c r="AF756">
+        <v>2</v>
+      </c>
+      <c r="AG756">
+        <v>11</v>
+      </c>
+      <c r="AH756">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="757" spans="1:34">
+      <c r="A757" s="2">
+        <v>46100</v>
+      </c>
+      <c r="B757">
+        <v>71246.55</v>
+      </c>
+      <c r="C757">
+        <v>71613.79</v>
+      </c>
+      <c r="D757">
+        <v>68793.35</v>
+      </c>
+      <c r="E757">
+        <v>69930</v>
+      </c>
+      <c r="F757">
+        <v>22364.81819</v>
+      </c>
+      <c r="G757">
+        <v>4972526</v>
+      </c>
+      <c r="H757">
+        <v>10489.13676</v>
+      </c>
+      <c r="I757">
+        <v>734634623.287388</v>
+      </c>
+      <c r="J757">
+        <v>1566573949.86041</v>
+      </c>
+      <c r="K757">
+        <v>11</v>
+      </c>
+      <c r="L757">
+        <v>0.474432153871211</v>
+      </c>
+      <c r="M757">
+        <v>3.75405773714803</v>
+      </c>
+      <c r="N757">
+        <v>1.41280404414281</v>
+      </c>
+      <c r="O757">
+        <v>-1.03463704220187</v>
+      </c>
+      <c r="P757">
+        <v>-0.066364350247516</v>
+      </c>
+      <c r="Q757">
+        <v>1.22786937169267</v>
+      </c>
+      <c r="R757">
+        <v>0.939486508715966</v>
+      </c>
+      <c r="S757">
+        <v>0.0243489489080614</v>
+      </c>
+      <c r="T757">
+        <v>-0.0383979050581093</v>
+      </c>
+      <c r="U757">
+        <v>0.469001655675878</v>
+      </c>
+      <c r="V757">
+        <v>0.468943469507359</v>
+      </c>
+      <c r="W757">
+        <v>-1.35598083389844</v>
+      </c>
+      <c r="X757">
+        <v>1.14950689171407</v>
+      </c>
+      <c r="Y757">
+        <v>0.900654746208655</v>
+      </c>
+      <c r="Z757">
+        <v>0.867656928725349</v>
+      </c>
+      <c r="AA757">
+        <v>-0.889390478325229</v>
+      </c>
+      <c r="AB757">
+        <v>0.23</v>
+      </c>
+      <c r="AC757">
+        <v>7</v>
+      </c>
+      <c r="AD757">
+        <v>1</v>
+      </c>
+      <c r="AE757">
+        <v>11</v>
+      </c>
+      <c r="AF757">
+        <v>2</v>
+      </c>
+      <c r="AG757">
+        <v>11</v>
+      </c>
+      <c r="AH757">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="758" spans="1:34">
+      <c r="A758" s="2">
+        <v>46101</v>
+      </c>
+      <c r="B758">
+        <v>69930.01</v>
+      </c>
+      <c r="C758">
+        <v>71367</v>
+      </c>
+      <c r="D758">
+        <v>69388</v>
+      </c>
+      <c r="E758">
+        <v>70510.73</v>
+      </c>
+      <c r="F758">
+        <v>18121.16745</v>
+      </c>
+      <c r="G758">
+        <v>4369971</v>
+      </c>
+      <c r="H758">
+        <v>8801.41211</v>
+      </c>
+      <c r="I758">
+        <v>618781938.226815</v>
+      </c>
+      <c r="J758">
+        <v>1273812840.68867</v>
+      </c>
+      <c r="K758">
+        <v>12</v>
+      </c>
+      <c r="L758">
+        <v>0.572226216859162</v>
+      </c>
+      <c r="M758">
+        <v>3.64050602233331</v>
+      </c>
+      <c r="N758">
+        <v>1.29298091095882</v>
+      </c>
+      <c r="O758">
+        <v>-1.74789875818067</v>
+      </c>
+      <c r="P758">
+        <v>-0.142264658709886</v>
+      </c>
+      <c r="Q758">
+        <v>1.01998517155518</v>
+      </c>
+      <c r="R758">
+        <v>0.758430352884638</v>
+      </c>
+      <c r="S758">
+        <v>-0.505825688323524</v>
+      </c>
+      <c r="T758">
+        <v>-0.346441644805086</v>
+      </c>
+      <c r="U758">
+        <v>0.485697852209848</v>
+      </c>
+      <c r="V758">
+        <v>0.485771471649068</v>
+      </c>
+      <c r="W758">
+        <v>-1.01743341585382</v>
+      </c>
+      <c r="X758">
+        <v>1.24222055721226</v>
+      </c>
+      <c r="Y758">
+        <v>1.03430905863835</v>
+      </c>
+      <c r="Z758">
+        <v>0.99279999983973</v>
+      </c>
+      <c r="AA758">
+        <v>-1.20192298730591</v>
+      </c>
+      <c r="AB758">
+        <v>0.11</v>
+      </c>
+      <c r="AC758">
+        <v>7</v>
+      </c>
+      <c r="AD758">
+        <v>1</v>
+      </c>
+      <c r="AE758">
+        <v>11</v>
+      </c>
+      <c r="AF758">
+        <v>2</v>
+      </c>
+      <c r="AG758">
+        <v>11</v>
+      </c>
+      <c r="AH758">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="759" spans="1:34">
+      <c r="A759" s="2">
+        <v>46102</v>
+      </c>
+      <c r="B759">
+        <v>70510.73</v>
+      </c>
+      <c r="C759">
+        <v>71100.94</v>
+      </c>
+      <c r="D759">
+        <v>68571.42</v>
+      </c>
+      <c r="E759">
+        <v>68918.12</v>
+      </c>
+      <c r="F759">
+        <v>13397.1675</v>
+      </c>
+      <c r="G759">
+        <v>1640086</v>
+      </c>
+      <c r="H759">
+        <v>6379.69313</v>
+      </c>
+      <c r="I759">
+        <v>449156360.934155</v>
+      </c>
+      <c r="J759">
+        <v>942693882.026424</v>
+      </c>
+      <c r="K759">
+        <v>10</v>
+      </c>
+      <c r="L759">
+        <v>0.547746837137307</v>
+      </c>
+      <c r="M759">
+        <v>3.36748049317246</v>
+      </c>
+      <c r="N759">
+        <v>1.11996078376814</v>
+      </c>
+      <c r="O759">
+        <v>-2.49121607994247</v>
+      </c>
+      <c r="P759">
+        <v>-0.256221285743433</v>
+      </c>
+      <c r="Q759">
+        <v>0.649147015820413</v>
+      </c>
+      <c r="R759">
+        <v>0.56161264565166</v>
+      </c>
+      <c r="S759">
+        <v>-1.23225860993146</v>
+      </c>
+      <c r="T759">
+        <v>-1.62285086102037</v>
+      </c>
+      <c r="U759">
+        <v>0.476197161079012</v>
+      </c>
+      <c r="V759">
+        <v>0.476460460280748</v>
+      </c>
+      <c r="W759">
+        <v>-1.58775203710403</v>
+      </c>
+      <c r="X759">
+        <v>0.942973733767168</v>
+      </c>
+      <c r="Y759">
+        <v>0.616679736627723</v>
+      </c>
+      <c r="Z759">
+        <v>0.557528032480067</v>
+      </c>
+      <c r="AA759">
+        <v>-1.04794533065895</v>
+      </c>
+      <c r="AB759">
+        <v>0.12</v>
+      </c>
+      <c r="AC759">
+        <v>7</v>
+      </c>
+      <c r="AD759">
+        <v>1</v>
+      </c>
+      <c r="AE759">
+        <v>11</v>
+      </c>
+      <c r="AF759">
+        <v>7</v>
+      </c>
+      <c r="AG759">
+        <v>7</v>
+      </c>
+      <c r="AH759">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="760" spans="1:34">
+      <c r="A760" s="2">
+        <v>46103</v>
+      </c>
+      <c r="B760">
+        <v>68918.12</v>
+      </c>
+      <c r="C760">
+        <v>69588.79</v>
+      </c>
+      <c r="D760">
+        <v>67360.66</v>
+      </c>
+      <c r="E760">
+        <v>67859</v>
+      </c>
+      <c r="F760">
+        <v>14843.78682</v>
+      </c>
+      <c r="G760">
+        <v>3269152</v>
+      </c>
+      <c r="H760">
+        <v>7292.32333</v>
+      </c>
+      <c r="I760">
+        <v>500700088.251835</v>
+      </c>
+      <c r="J760">
+        <v>1018926475.3197</v>
+      </c>
+      <c r="K760">
+        <v>8</v>
+      </c>
+      <c r="L760">
+        <v>0.555196893676245</v>
+      </c>
+      <c r="M760">
+        <v>3.43085373755613</v>
+      </c>
+      <c r="N760">
+        <v>0.924995428629553</v>
+      </c>
+      <c r="O760">
+        <v>-2.81944368212295</v>
+      </c>
+      <c r="P760">
+        <v>-1.07523847068755</v>
+      </c>
+      <c r="Q760">
+        <v>-0.0672651093016003</v>
+      </c>
+      <c r="R760">
+        <v>0.640613219249673</v>
+      </c>
+      <c r="S760">
+        <v>-0.91899232926178</v>
+      </c>
+      <c r="T760">
+        <v>-0.783778871712749</v>
+      </c>
+      <c r="U760">
+        <v>0.491271089946844</v>
+      </c>
+      <c r="V760">
+        <v>0.491399625370157</v>
+      </c>
+      <c r="W760">
+        <v>-1.64364124325697</v>
+      </c>
+      <c r="X760">
+        <v>0.748998527704469</v>
+      </c>
+      <c r="Y760">
+        <v>0.341532572856359</v>
+      </c>
+      <c r="Z760">
+        <v>0.273627201489374</v>
+      </c>
+      <c r="AA760">
+        <v>-1.05714611938826</v>
+      </c>
+      <c r="AB760">
+        <v>0.1</v>
+      </c>
+      <c r="AC760">
+        <v>4</v>
+      </c>
+      <c r="AD760">
+        <v>8</v>
+      </c>
+      <c r="AE760">
+        <v>2</v>
+      </c>
+      <c r="AF760">
+        <v>7</v>
+      </c>
+      <c r="AG760">
+        <v>7</v>
+      </c>
+      <c r="AH760">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="761" spans="1:34">
+      <c r="A761" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B761">
+        <v>67859</v>
+      </c>
+      <c r="C761">
+        <v>71817.09</v>
+      </c>
+      <c r="D761">
+        <v>67445.18</v>
+      </c>
+      <c r="E761">
+        <v>70906.45</v>
+      </c>
+      <c r="F761">
+        <v>28335.09119</v>
+      </c>
+      <c r="G761">
+        <v>6509730</v>
+      </c>
+      <c r="H761">
+        <v>14640.9723</v>
+      </c>
+      <c r="I761">
+        <v>1022970775.45578</v>
+      </c>
+      <c r="J761">
+        <v>1980755169.23169</v>
+      </c>
+      <c r="K761">
+        <v>11</v>
+      </c>
+      <c r="L761">
+        <v>0.569946215007669</v>
+      </c>
+      <c r="M761">
+        <v>3.35297357253655</v>
+      </c>
+      <c r="N761">
+        <v>0.905545411817484</v>
+      </c>
+      <c r="O761">
+        <v>-2.26221135134131</v>
+      </c>
+      <c r="P761">
+        <v>-5.07428253748454</v>
+      </c>
+      <c r="Q761">
+        <v>-0.454626637747307</v>
+      </c>
+      <c r="R761">
+        <v>1.18815591825428</v>
+      </c>
+      <c r="S761">
+        <v>0.635180412908529</v>
+      </c>
+      <c r="T761">
+        <v>0.740477740061066</v>
+      </c>
+      <c r="U761">
+        <v>0.516708141217032</v>
+      </c>
+      <c r="V761">
+        <v>0.516454931607008</v>
+      </c>
+      <c r="W761">
+        <v>0.106400936846599</v>
+      </c>
+      <c r="X761">
+        <v>1.27766864498263</v>
+      </c>
+      <c r="Y761">
+        <v>1.15002217552928</v>
+      </c>
+      <c r="Z761">
+        <v>1.08903185894179</v>
+      </c>
+      <c r="AA761">
+        <v>-0.768706028809944</v>
+      </c>
+      <c r="AB761">
+        <v>0.08</v>
+      </c>
+      <c r="AC761">
+        <v>4</v>
+      </c>
+      <c r="AD761">
+        <v>8</v>
+      </c>
+      <c r="AE761">
+        <v>2</v>
+      </c>
+      <c r="AF761">
+        <v>2</v>
+      </c>
+      <c r="AG761">
+        <v>2</v>
+      </c>
+      <c r="AH761">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="762" spans="1:34">
+      <c r="A762" s="2">
+        <v>46105</v>
+      </c>
+      <c r="B762">
+        <v>70906.45</v>
+      </c>
+      <c r="C762">
+        <v>71400</v>
+      </c>
+      <c r="D762">
+        <v>68923.07</v>
+      </c>
+      <c r="E762">
+        <v>70556.74</v>
+      </c>
+      <c r="F762">
+        <v>20702.42244</v>
+      </c>
+      <c r="G762">
+        <v>4191328</v>
+      </c>
+      <c r="H762">
+        <v>9731.85043</v>
+      </c>
+      <c r="I762">
+        <v>684254039.294913</v>
+      </c>
+      <c r="J762">
+        <v>1455361229.20996</v>
+      </c>
+      <c r="K762">
+        <v>14</v>
+      </c>
+      <c r="L762">
+        <v>0.518404898691491</v>
+      </c>
+      <c r="M762">
+        <v>3.25726670902508</v>
+      </c>
+      <c r="N762">
+        <v>0.863100936767714</v>
+      </c>
+      <c r="O762">
+        <v>-1.9639716147358</v>
+      </c>
+      <c r="P762">
+        <v>-0.0612802467065062</v>
+      </c>
+      <c r="Q762">
+        <v>-0.580247976438141</v>
+      </c>
+      <c r="R762">
+        <v>0.85316165383164</v>
+      </c>
+      <c r="S762">
+        <v>-0.366897622911165</v>
+      </c>
+      <c r="T762">
+        <v>-0.481801435092084</v>
+      </c>
+      <c r="U762">
+        <v>0.470082689994611</v>
+      </c>
+      <c r="V762">
+        <v>0.470160964550608</v>
+      </c>
+      <c r="W762">
+        <v>0.162324906438</v>
+      </c>
+      <c r="X762">
+        <v>1.15921341206131</v>
+      </c>
+      <c r="Y762">
+        <v>1.02710574824495</v>
+      </c>
+      <c r="Z762">
+        <v>0.96808086728961</v>
+      </c>
+      <c r="AA762">
+        <v>-0.892621875666392</v>
+      </c>
+      <c r="AB762">
+        <v>0.11</v>
+      </c>
+      <c r="AC762">
+        <v>7</v>
+      </c>
+      <c r="AD762">
+        <v>1</v>
+      </c>
+      <c r="AE762">
+        <v>6</v>
+      </c>
+      <c r="AF762">
+        <v>7</v>
+      </c>
+      <c r="AG762">
+        <v>7</v>
+      </c>
+      <c r="AH762">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="763" spans="1:34">
+      <c r="A763" s="2">
+        <v>46106</v>
+      </c>
+      <c r="B763">
+        <v>70556.74</v>
+      </c>
+      <c r="C763">
+        <v>72026.09</v>
+      </c>
+      <c r="D763">
+        <v>70408</v>
+      </c>
+      <c r="E763">
+        <v>71336.53</v>
+      </c>
+      <c r="F763">
+        <v>17719.50066</v>
+      </c>
+      <c r="G763">
+        <v>3298902</v>
+      </c>
+      <c r="H763">
+        <v>8819.77787</v>
+      </c>
+      <c r="I763">
+        <v>627874982.892166</v>
+      </c>
+      <c r="J763">
+        <v>1261017988.53943</v>
+      </c>
+      <c r="K763">
+        <v>10</v>
+      </c>
+      <c r="L763">
+        <v>0.533554475640049</v>
+      </c>
+      <c r="M763">
+        <v>3.43066213697296</v>
+      </c>
+      <c r="N763">
+        <v>0.863367693425726</v>
+      </c>
+      <c r="O763">
+        <v>-1.64282179796739</v>
+      </c>
+      <c r="P763">
+        <v>0.104958259312372</v>
+      </c>
+      <c r="Q763">
+        <v>-0.672450352133338</v>
+      </c>
+      <c r="R763">
+        <v>0.745969502898082</v>
+      </c>
+      <c r="S763">
+        <v>-0.811111194546956</v>
+      </c>
+      <c r="T763">
+        <v>-0.894443239106472</v>
+      </c>
+      <c r="U763">
+        <v>0.497744154264446</v>
+      </c>
+      <c r="V763">
+        <v>0.497911202376582</v>
+      </c>
+      <c r="W763">
+        <v>0.491140775579383</v>
+      </c>
+      <c r="X763">
+        <v>1.27851988251129</v>
+      </c>
+      <c r="Y763">
+        <v>1.22308523499878</v>
+      </c>
+      <c r="Z763">
+        <v>1.17245063637134</v>
+      </c>
+      <c r="AA763">
+        <v>-1.3200846836316</v>
+      </c>
+      <c r="AB763">
+        <v>0.14</v>
+      </c>
+      <c r="AC763">
+        <v>7</v>
+      </c>
+      <c r="AD763">
+        <v>1</v>
+      </c>
+      <c r="AE763">
+        <v>6</v>
+      </c>
+      <c r="AF763">
+        <v>7</v>
+      </c>
+      <c r="AG763">
+        <v>7</v>
+      </c>
+      <c r="AH763">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="764" spans="1:34">
+      <c r="A764" s="2">
+        <v>46107</v>
+      </c>
+      <c r="B764">
+        <v>71336.53</v>
+      </c>
+      <c r="C764">
+        <v>71436.82</v>
+      </c>
+      <c r="D764">
+        <v>68153</v>
+      </c>
+      <c r="E764">
+        <v>68820.31</v>
+      </c>
+      <c r="F764">
+        <v>20820.45768</v>
+      </c>
+      <c r="G764">
+        <v>3597702</v>
+      </c>
+      <c r="H764">
+        <v>10116.39467</v>
+      </c>
+      <c r="I764">
+        <v>703650001.59012</v>
+      </c>
+      <c r="J764">
+        <v>1447699734.33984</v>
+      </c>
+      <c r="K764">
+        <v>13</v>
+      </c>
+      <c r="L764">
+        <v>0.45523660203614</v>
+      </c>
+      <c r="M764">
+        <v>3.69223300087415</v>
+      </c>
+      <c r="N764">
+        <v>0.720519407020456</v>
+      </c>
+      <c r="O764">
+        <v>-1.84401253741695</v>
+      </c>
+      <c r="P764">
+        <v>-0.0907108876265881</v>
+      </c>
+      <c r="Q764">
+        <v>-0.406121855968879</v>
+      </c>
+      <c r="R764">
+        <v>0.879332401264697</v>
+      </c>
+      <c r="S764">
+        <v>-0.2732351531999</v>
+      </c>
+      <c r="T764">
+        <v>-0.679894339708558</v>
+      </c>
+      <c r="U764">
+        <v>0.485887237710329</v>
+      </c>
+      <c r="V764">
+        <v>0.486046923197778</v>
+      </c>
+      <c r="W764">
+        <v>-0.755655767025095</v>
+      </c>
+      <c r="X764">
+        <v>0.755099650867726</v>
+      </c>
+      <c r="Y764">
+        <v>0.49724726146107</v>
+      </c>
+      <c r="Z764">
+        <v>0.43232867880637</v>
+      </c>
+      <c r="AA764">
+        <v>-0.840546680251106</v>
+      </c>
+      <c r="AB764">
+        <v>0.1</v>
+      </c>
+      <c r="AC764">
+        <v>7</v>
+      </c>
+      <c r="AD764">
+        <v>3</v>
+      </c>
+      <c r="AE764">
+        <v>6</v>
+      </c>
+      <c r="AF764">
+        <v>7</v>
+      </c>
+      <c r="AG764">
+        <v>7</v>
+      </c>
+      <c r="AH764">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="765" spans="1:34">
+      <c r="A765" s="2">
+        <v>46108</v>
+      </c>
+      <c r="B765">
+        <v>68820.31</v>
+      </c>
+      <c r="C765">
+        <v>69179.05</v>
+      </c>
+      <c r="D765">
+        <v>65548.25</v>
+      </c>
+      <c r="E765">
+        <v>66407.28</v>
+      </c>
+      <c r="F765">
+        <v>28603.69557</v>
+      </c>
+      <c r="G765">
+        <v>4159306</v>
+      </c>
+      <c r="H765">
+        <v>14568.62853</v>
+      </c>
+      <c r="I765">
+        <v>976680026.265681</v>
+      </c>
+      <c r="J765">
+        <v>1917318222.70991</v>
+      </c>
+      <c r="K765">
+        <v>12</v>
+      </c>
+      <c r="L765">
+        <v>0.393573042168675</v>
+      </c>
+      <c r="M765">
+        <v>3.72585774786759</v>
+      </c>
+      <c r="N765">
+        <v>0.444572751597115</v>
+      </c>
+      <c r="O765">
+        <v>-2.17046809652396</v>
+      </c>
+      <c r="P765">
+        <v>-0.0093917549479008</v>
+      </c>
+      <c r="Q765">
+        <v>0.636660291978198</v>
+      </c>
+      <c r="R765">
+        <v>1.211711375649</v>
+      </c>
+      <c r="S765">
+        <v>0.775190973329461</v>
+      </c>
+      <c r="T765">
+        <v>-0.32020464374312</v>
+      </c>
+      <c r="U765">
+        <v>0.509326792908529</v>
+      </c>
+      <c r="V765">
+        <v>0.509399021350382</v>
+      </c>
+      <c r="W765">
+        <v>-1.58395776750051</v>
+      </c>
+      <c r="X765">
+        <v>0.208560554322585</v>
+      </c>
+      <c r="Y765">
+        <v>-0.250893984040821</v>
+      </c>
+      <c r="Z765">
+        <v>-0.327002824476324</v>
+      </c>
+      <c r="AA765">
+        <v>-0.253950601866573</v>
+      </c>
+      <c r="AB765">
+        <v>0.13</v>
+      </c>
+      <c r="AC765">
+        <v>5</v>
+      </c>
+      <c r="AD765">
+        <v>9</v>
+      </c>
+      <c r="AE765">
+        <v>3</v>
+      </c>
+      <c r="AF765">
+        <v>5</v>
+      </c>
+      <c r="AG765">
+        <v>13</v>
+      </c>
+      <c r="AH765">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="766" spans="1:34">
+      <c r="A766" s="2">
+        <v>46109</v>
+      </c>
+      <c r="B766">
+        <v>66407.28</v>
+      </c>
+      <c r="C766">
+        <v>67288.94</v>
+      </c>
+      <c r="D766">
+        <v>65932.09</v>
+      </c>
+      <c r="E766">
+        <v>66377.03</v>
+      </c>
+      <c r="F766">
+        <v>11462.39847</v>
+      </c>
+      <c r="G766">
+        <v>1687368</v>
+      </c>
+      <c r="H766">
+        <v>5753.04124</v>
+      </c>
+      <c r="I766">
+        <v>382921412.223849</v>
+      </c>
+      <c r="J766">
+        <v>762676255.44706</v>
+      </c>
+      <c r="K766">
+        <v>9</v>
+      </c>
+      <c r="L766">
+        <v>0.384862571024419</v>
+      </c>
+      <c r="M766">
+        <v>3.59326197154135</v>
+      </c>
+      <c r="N766">
+        <v>0.195336220597572</v>
+      </c>
+      <c r="O766">
+        <v>-2.18381943825835</v>
+      </c>
+      <c r="P766">
+        <v>0.00634636239195084</v>
+      </c>
+      <c r="Q766">
+        <v>1.37103121530108</v>
+      </c>
+      <c r="R766">
+        <v>0.492014926309771</v>
+      </c>
+      <c r="S766">
+        <v>-2.00364291795875</v>
+      </c>
+      <c r="T766">
+        <v>-1.59631274882261</v>
+      </c>
+      <c r="U766">
+        <v>0.501905535308092</v>
+      </c>
+      <c r="V766">
+        <v>0.502075958821336</v>
+      </c>
+      <c r="W766">
+        <v>-1.32535537843813</v>
+      </c>
+      <c r="X766">
+        <v>0.13226486758981</v>
+      </c>
+      <c r="Y766">
+        <v>-0.256382984382753</v>
+      </c>
+      <c r="Z766">
+        <v>-0.331860664137028</v>
+      </c>
+      <c r="AA766">
+        <v>-0.750578909742314</v>
+      </c>
+      <c r="AB766">
+        <v>0.12</v>
+      </c>
+      <c r="AC766">
+        <v>0</v>
+      </c>
+      <c r="AD766">
+        <v>9</v>
+      </c>
+      <c r="AE766">
+        <v>3</v>
+      </c>
+      <c r="AF766">
+        <v>3</v>
+      </c>
+      <c r="AG766">
+        <v>4</v>
+      </c>
+      <c r="AH766">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/btc.xlsx
+++ b/btc.xlsx
@@ -145,7 +145,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,13 +156,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -630,28 +623,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -660,118 +656,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/btc.xlsx
+++ b/btc.xlsx
@@ -1120,10 +1120,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH766"/>
+  <dimension ref="A1:AH765"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="27.1818181818182" customWidth="1"/>
+    <col min="2" max="5" width="9.54545454545454"/>
+    <col min="6" max="6" width="12.8181818181818"/>
+    <col min="8" max="9" width="12.8181818181818"/>
+    <col min="10" max="10" width="11.7272727272727"/>
+    <col min="12" max="14" width="12.8181818181818"/>
+    <col min="15" max="16" width="14"/>
+    <col min="17" max="19" width="12.8181818181818"/>
+    <col min="20" max="20" width="14"/>
+    <col min="21" max="22" width="12.8181818181818"/>
+    <col min="23" max="23" width="14"/>
+    <col min="24" max="24" width="12.8181818181818"/>
+    <col min="25" max="27" width="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
@@ -80684,110 +80696,6 @@
       </c>
       <c r="AH765">
         <v>12</v>
-      </c>
-    </row>
-    <row r="766" spans="1:34">
-      <c r="A766" s="2">
-        <v>46109</v>
-      </c>
-      <c r="B766">
-        <v>66407.28</v>
-      </c>
-      <c r="C766">
-        <v>67288.94</v>
-      </c>
-      <c r="D766">
-        <v>65932.09</v>
-      </c>
-      <c r="E766">
-        <v>66377.03</v>
-      </c>
-      <c r="F766">
-        <v>11462.39847</v>
-      </c>
-      <c r="G766">
-        <v>1687368</v>
-      </c>
-      <c r="H766">
-        <v>5753.04124</v>
-      </c>
-      <c r="I766">
-        <v>382921412.223849</v>
-      </c>
-      <c r="J766">
-        <v>762676255.44706</v>
-      </c>
-      <c r="K766">
-        <v>9</v>
-      </c>
-      <c r="L766">
-        <v>0.384862571024419</v>
-      </c>
-      <c r="M766">
-        <v>3.59326197154135</v>
-      </c>
-      <c r="N766">
-        <v>0.195336220597572</v>
-      </c>
-      <c r="O766">
-        <v>-2.18381943825835</v>
-      </c>
-      <c r="P766">
-        <v>0.00634636239195084</v>
-      </c>
-      <c r="Q766">
-        <v>1.37103121530108</v>
-      </c>
-      <c r="R766">
-        <v>0.492014926309771</v>
-      </c>
-      <c r="S766">
-        <v>-2.00364291795875</v>
-      </c>
-      <c r="T766">
-        <v>-1.59631274882261</v>
-      </c>
-      <c r="U766">
-        <v>0.501905535308092</v>
-      </c>
-      <c r="V766">
-        <v>0.502075958821336</v>
-      </c>
-      <c r="W766">
-        <v>-1.32535537843813</v>
-      </c>
-      <c r="X766">
-        <v>0.13226486758981</v>
-      </c>
-      <c r="Y766">
-        <v>-0.256382984382753</v>
-      </c>
-      <c r="Z766">
-        <v>-0.331860664137028</v>
-      </c>
-      <c r="AA766">
-        <v>-0.750578909742314</v>
-      </c>
-      <c r="AB766">
-        <v>0.12</v>
-      </c>
-      <c r="AC766">
-        <v>0</v>
-      </c>
-      <c r="AD766">
-        <v>9</v>
-      </c>
-      <c r="AE766">
-        <v>3</v>
-      </c>
-      <c r="AF766">
-        <v>3</v>
-      </c>
-      <c r="AG766">
-        <v>4</v>
-      </c>
-      <c r="AH766">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/btc.xlsx
+++ b/btc.xlsx
@@ -145,7 +145,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,6 +156,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -623,31 +630,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -656,115 +660,118 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1120,22 +1127,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH765"/>
+  <dimension ref="A1:AH766"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="27.1818181818182" customWidth="1"/>
-    <col min="2" max="5" width="9.54545454545454"/>
-    <col min="6" max="6" width="12.8181818181818"/>
-    <col min="8" max="9" width="12.8181818181818"/>
-    <col min="10" max="10" width="11.7272727272727"/>
-    <col min="12" max="14" width="12.8181818181818"/>
-    <col min="15" max="16" width="14"/>
-    <col min="17" max="19" width="12.8181818181818"/>
-    <col min="20" max="20" width="14"/>
-    <col min="21" max="22" width="12.8181818181818"/>
-    <col min="23" max="23" width="14"/>
-    <col min="24" max="24" width="12.8181818181818"/>
-    <col min="25" max="27" width="14"/>
+    <col min="1" max="1" width="28.9090909090909" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
@@ -80696,6 +80691,110 @@
       </c>
       <c r="AH765">
         <v>12</v>
+      </c>
+    </row>
+    <row r="766" spans="1:34">
+      <c r="A766" s="2">
+        <v>46109</v>
+      </c>
+      <c r="B766">
+        <v>66407.28</v>
+      </c>
+      <c r="C766">
+        <v>67288.94</v>
+      </c>
+      <c r="D766">
+        <v>65932.09</v>
+      </c>
+      <c r="E766">
+        <v>66377.03</v>
+      </c>
+      <c r="F766">
+        <v>11462.39847</v>
+      </c>
+      <c r="G766">
+        <v>1687368</v>
+      </c>
+      <c r="H766">
+        <v>5753.04124</v>
+      </c>
+      <c r="I766">
+        <v>382921412.223849</v>
+      </c>
+      <c r="J766">
+        <v>762676255.44706</v>
+      </c>
+      <c r="K766">
+        <v>9</v>
+      </c>
+      <c r="L766">
+        <v>0.384862571024419</v>
+      </c>
+      <c r="M766">
+        <v>3.59326197154135</v>
+      </c>
+      <c r="N766">
+        <v>0.195336220597572</v>
+      </c>
+      <c r="O766">
+        <v>-2.18381943825835</v>
+      </c>
+      <c r="P766">
+        <v>0.00634636239195084</v>
+      </c>
+      <c r="Q766">
+        <v>1.37103121530108</v>
+      </c>
+      <c r="R766">
+        <v>0.492014926309771</v>
+      </c>
+      <c r="S766">
+        <v>-2.00364291795875</v>
+      </c>
+      <c r="T766">
+        <v>-1.59631274882261</v>
+      </c>
+      <c r="U766">
+        <v>0.501905535308092</v>
+      </c>
+      <c r="V766">
+        <v>0.502075958821336</v>
+      </c>
+      <c r="W766">
+        <v>-1.32535537843813</v>
+      </c>
+      <c r="X766">
+        <v>0.13226486758981</v>
+      </c>
+      <c r="Y766">
+        <v>-0.256382984382753</v>
+      </c>
+      <c r="Z766">
+        <v>-0.331860664137028</v>
+      </c>
+      <c r="AA766">
+        <v>-0.750578909742314</v>
+      </c>
+      <c r="AB766">
+        <v>0.12</v>
+      </c>
+      <c r="AC766">
+        <v>0</v>
+      </c>
+      <c r="AD766">
+        <v>9</v>
+      </c>
+      <c r="AE766">
+        <v>3</v>
+      </c>
+      <c r="AF766">
+        <v>3</v>
+      </c>
+      <c r="AG766">
+        <v>4</v>
+      </c>
+      <c r="AH766">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/btc.xlsx
+++ b/btc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="7140"/>
+    <workbookView windowWidth="14930" windowHeight="7140"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -145,7 +145,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,13 +156,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -630,28 +623,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -660,118 +656,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1127,10 +1120,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH766"/>
+  <dimension ref="A1:AH765"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="28.9090909090909" customWidth="1"/>
+    <col min="2" max="5" width="9.54545454545454"/>
+    <col min="6" max="6" width="12.8181818181818"/>
+    <col min="8" max="9" width="12.8181818181818"/>
+    <col min="10" max="10" width="11.7272727272727"/>
+    <col min="12" max="14" width="12.8181818181818"/>
+    <col min="15" max="16" width="14"/>
+    <col min="17" max="19" width="12.8181818181818"/>
+    <col min="20" max="20" width="14"/>
+    <col min="21" max="22" width="12.8181818181818"/>
+    <col min="23" max="23" width="14"/>
+    <col min="24" max="24" width="12.8181818181818"/>
+    <col min="25" max="27" width="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
@@ -80691,110 +80696,6 @@
       </c>
       <c r="AH765">
         <v>12</v>
-      </c>
-    </row>
-    <row r="766" spans="1:34">
-      <c r="A766" s="2">
-        <v>46109</v>
-      </c>
-      <c r="B766">
-        <v>66407.28</v>
-      </c>
-      <c r="C766">
-        <v>67288.94</v>
-      </c>
-      <c r="D766">
-        <v>65932.09</v>
-      </c>
-      <c r="E766">
-        <v>66377.03</v>
-      </c>
-      <c r="F766">
-        <v>11462.39847</v>
-      </c>
-      <c r="G766">
-        <v>1687368</v>
-      </c>
-      <c r="H766">
-        <v>5753.04124</v>
-      </c>
-      <c r="I766">
-        <v>382921412.223849</v>
-      </c>
-      <c r="J766">
-        <v>762676255.44706</v>
-      </c>
-      <c r="K766">
-        <v>9</v>
-      </c>
-      <c r="L766">
-        <v>0.384862571024419</v>
-      </c>
-      <c r="M766">
-        <v>3.59326197154135</v>
-      </c>
-      <c r="N766">
-        <v>0.195336220597572</v>
-      </c>
-      <c r="O766">
-        <v>-2.18381943825835</v>
-      </c>
-      <c r="P766">
-        <v>0.00634636239195084</v>
-      </c>
-      <c r="Q766">
-        <v>1.37103121530108</v>
-      </c>
-      <c r="R766">
-        <v>0.492014926309771</v>
-      </c>
-      <c r="S766">
-        <v>-2.00364291795875</v>
-      </c>
-      <c r="T766">
-        <v>-1.59631274882261</v>
-      </c>
-      <c r="U766">
-        <v>0.501905535308092</v>
-      </c>
-      <c r="V766">
-        <v>0.502075958821336</v>
-      </c>
-      <c r="W766">
-        <v>-1.32535537843813</v>
-      </c>
-      <c r="X766">
-        <v>0.13226486758981</v>
-      </c>
-      <c r="Y766">
-        <v>-0.256382984382753</v>
-      </c>
-      <c r="Z766">
-        <v>-0.331860664137028</v>
-      </c>
-      <c r="AA766">
-        <v>-0.750578909742314</v>
-      </c>
-      <c r="AB766">
-        <v>0.12</v>
-      </c>
-      <c r="AC766">
-        <v>0</v>
-      </c>
-      <c r="AD766">
-        <v>9</v>
-      </c>
-      <c r="AE766">
-        <v>3</v>
-      </c>
-      <c r="AF766">
-        <v>3</v>
-      </c>
-      <c r="AG766">
-        <v>4</v>
-      </c>
-      <c r="AH766">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
